--- a/Output/Models/Exposure_models_malf_iqr_Masculino.xlsx
+++ b/Output/Models/Exposure_models_malf_iqr_Masculino.xlsx
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.7153927966155889</v>
+        <v>0.6995903981965811</v>
       </c>
       <c r="C3">
-        <v>0.1595138465847177</v>
+        <v>0.1591600990581668</v>
       </c>
       <c r="D3">
-        <v>-2.099651713060051</v>
+        <v>-2.244659702718741</v>
       </c>
       <c r="E3">
-        <v>0.03575949015614112</v>
+        <v>0.02478998686477841</v>
       </c>
       <c r="F3">
-        <v>0.5233185513264217</v>
+        <v>0.5121138463199525</v>
       </c>
       <c r="G3">
-        <v>0.9779642860974073</v>
+        <v>0.9556990672403585</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -564,22 +564,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.6684350283631546</v>
+        <v>0.7331592644182332</v>
       </c>
       <c r="C4">
-        <v>0.1620386181386061</v>
+        <v>0.1562914476844667</v>
       </c>
       <c r="D4">
-        <v>-2.485926391948821</v>
+        <v>-1.98598405594673</v>
       </c>
       <c r="E4">
-        <v>0.0129214689056537</v>
+        <v>0.04703509432426414</v>
       </c>
       <c r="F4">
-        <v>0.4865547072539694</v>
+        <v>0.539712908495058</v>
       </c>
       <c r="G4">
-        <v>0.9183045205020079</v>
+        <v>0.9959415432569863</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.156137578146825</v>
+        <v>1.286039359708011</v>
       </c>
       <c r="C5">
-        <v>0.15097145316522</v>
+        <v>0.150416356905901</v>
       </c>
       <c r="D5">
-        <v>0.9610080075718117</v>
+        <v>1.672472574304349</v>
       </c>
       <c r="E5">
-        <v>0.3365481416008803</v>
+        <v>0.0944311715645853</v>
       </c>
       <c r="F5">
-        <v>0.8600077866847525</v>
+        <v>0.9576782526853476</v>
       </c>
       <c r="G5">
-        <v>1.554234880542046</v>
+        <v>1.726986313076059</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="O5">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="6">
@@ -812,26 +812,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B8">
-        <v>1.288713529859836</v>
+        <v>1.441561382033191</v>
       </c>
       <c r="C8">
-        <v>0.1597028898003805</v>
+        <v>0.2302736301774674</v>
       </c>
       <c r="D8">
-        <v>1.588227097316809</v>
+        <v>1.588227097316796</v>
       </c>
       <c r="E8">
-        <v>0.1122349957968474</v>
+        <v>0.1122349957968504</v>
       </c>
       <c r="F8">
-        <v>0.9423604303499041</v>
+        <v>0.9179602384896693</v>
       </c>
       <c r="G8">
-        <v>1.762364492986128</v>
+        <v>2.2638226919159</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,26 +875,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.7197293311555429</v>
+        <v>0.6003919459049309</v>
       </c>
       <c r="C9">
-        <v>0.1701843816153589</v>
+        <v>0.2463359434171505</v>
       </c>
       <c r="D9">
-        <v>-1.932492649913017</v>
+        <v>-2.071044066020111</v>
       </c>
       <c r="E9">
-        <v>0.05329872838455925</v>
+        <v>0.03835467820483612</v>
       </c>
       <c r="F9">
-        <v>0.5155941647909162</v>
+        <v>0.3704702364071443</v>
       </c>
       <c r="G9">
-        <v>1.004686137857415</v>
+        <v>0.973007959298935</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -938,26 +938,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.6430310688296004</v>
+        <v>0.6013639443457214</v>
       </c>
       <c r="C10">
-        <v>0.1747081446710547</v>
+        <v>0.2496169803000816</v>
       </c>
       <c r="D10">
-        <v>-2.527427889467738</v>
+        <v>-2.037341219658585</v>
       </c>
       <c r="E10">
-        <v>0.01149014171543323</v>
+        <v>0.04161585987417881</v>
       </c>
       <c r="F10">
-        <v>0.4565833965755413</v>
+        <v>0.3686914165176872</v>
       </c>
       <c r="G10">
-        <v>0.9056154003439039</v>
+        <v>0.9808706613642983</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1001,26 +1001,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B11">
-        <v>1.137618217495968</v>
+        <v>1.445724615121156</v>
       </c>
       <c r="C11">
-        <v>0.1617849575239614</v>
+        <v>0.2392191084551177</v>
       </c>
       <c r="D11">
-        <v>0.7969640434140465</v>
+        <v>1.540891369446309</v>
       </c>
       <c r="E11">
-        <v>0.4254719142223082</v>
+        <v>0.123343226686984</v>
       </c>
       <c r="F11">
-        <v>0.828485539520402</v>
+        <v>0.9046110765128137</v>
       </c>
       <c r="G11">
-        <v>1.562097522580638</v>
+        <v>2.310517433441584</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1058,32 +1058,32 @@
         </is>
       </c>
       <c r="O11">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.7315388377297314</v>
+        <v>0.6483499488444119</v>
       </c>
       <c r="C12">
-        <v>0.1434033279455018</v>
+        <v>0.1987818761004909</v>
       </c>
       <c r="D12">
-        <v>-2.179900363096382</v>
+        <v>-2.179900363096378</v>
       </c>
       <c r="E12">
-        <v>0.02926484802137136</v>
+        <v>0.02926484802137164</v>
       </c>
       <c r="F12">
-        <v>0.5522964527989156</v>
+        <v>0.4391430776427788</v>
       </c>
       <c r="G12">
-        <v>0.9689525768180292</v>
+        <v>0.9572225490219195</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.685057263678593</v>
+        <v>0.1798390221412867</v>
       </c>
       <c r="C13">
-        <v>0.1471784221302267</v>
+        <v>0.667577289183257</v>
       </c>
       <c r="D13">
-        <v>-2.570029234775616</v>
+        <v>-2.57002923477562</v>
       </c>
       <c r="E13">
-        <v>0.01016899329958383</v>
+        <v>0.01016899329958369</v>
       </c>
       <c r="F13">
-        <v>0.5133911471430828</v>
+        <v>0.04860054212175446</v>
       </c>
       <c r="G13">
-        <v>0.9141245561603069</v>
+        <v>0.6654673481565408</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1190,26 +1190,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B14">
-        <v>1.235114156208612</v>
+        <v>1.349571939908039</v>
       </c>
       <c r="C14">
-        <v>0.1501897967470648</v>
+        <v>0.2132235878990381</v>
       </c>
       <c r="D14">
-        <v>1.405977000826493</v>
+        <v>1.405977000826492</v>
       </c>
       <c r="E14">
-        <v>0.1597309543646708</v>
+        <v>0.159730954364671</v>
       </c>
       <c r="F14">
-        <v>0.9201641577820139</v>
+        <v>0.8885866676909553</v>
       </c>
       <c r="G14">
-        <v>1.657863943042544</v>
+        <v>2.049709372435238</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1253,26 +1253,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.7097617540257065</v>
+        <v>0.5906406319849749</v>
       </c>
       <c r="C15">
-        <v>0.1614367798623591</v>
+        <v>0.2322332811524928</v>
       </c>
       <c r="D15">
-        <v>-2.123592425848853</v>
+        <v>-2.267321512310516</v>
       </c>
       <c r="E15">
-        <v>0.03370423944730016</v>
+        <v>0.02337059225228851</v>
       </c>
       <c r="F15">
-        <v>0.5172462577496184</v>
+        <v>0.3746674744094021</v>
       </c>
       <c r="G15">
-        <v>0.9739301926888019</v>
+        <v>0.931109263491638</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1316,26 +1316,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.6579574378329455</v>
+        <v>0.6255890735551961</v>
       </c>
       <c r="C16">
-        <v>0.1663111225498256</v>
+        <v>0.2337241559245862</v>
       </c>
       <c r="D16">
-        <v>-2.517059758092699</v>
+        <v>-2.006902340037422</v>
       </c>
       <c r="E16">
-        <v>0.0118338756111681</v>
+        <v>0.04476006265006829</v>
       </c>
       <c r="F16">
-        <v>0.4749342790952951</v>
+        <v>0.3956788097296762</v>
       </c>
       <c r="G16">
-        <v>0.9115113586333313</v>
+        <v>0.9890893303561618</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,26 +1379,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B17">
-        <v>1.150682179498549</v>
+        <v>1.430926441310913</v>
       </c>
       <c r="C17">
-        <v>0.15135903765758</v>
+        <v>0.2223072868176574</v>
       </c>
       <c r="D17">
-        <v>0.9272982191081777</v>
+        <v>1.611832435573408</v>
       </c>
       <c r="E17">
-        <v>0.3537717187356944</v>
+        <v>0.1069984078882004</v>
       </c>
       <c r="F17">
-        <v>0.8552997416290513</v>
+        <v>0.9255268092192366</v>
       </c>
       <c r="G17">
-        <v>1.54807655582081</v>
+        <v>2.212308125542038</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1436,32 +1436,32 @@
         </is>
       </c>
       <c r="O17">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.7526564803839932</v>
+        <v>0.6721684158709238</v>
       </c>
       <c r="C18">
-        <v>0.1324307337571345</v>
+        <v>0.1851427073389547</v>
       </c>
       <c r="D18">
-        <v>-2.145622459089551</v>
+        <v>-2.145622459089553</v>
       </c>
       <c r="E18">
-        <v>0.03190311211064385</v>
+        <v>0.03190311211064371</v>
       </c>
       <c r="F18">
-        <v>0.5805926857392361</v>
+        <v>0.4676105959344278</v>
       </c>
       <c r="G18">
-        <v>0.9757129074796014</v>
+        <v>0.9662107386415678</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1505,26 +1505,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.6916878089077317</v>
+        <v>0.2037188777234697</v>
       </c>
       <c r="C19">
-        <v>0.140560264590979</v>
+        <v>0.6066763718327489</v>
       </c>
       <c r="D19">
-        <v>-2.622509067052185</v>
+        <v>-2.622509067052184</v>
       </c>
       <c r="E19">
-        <v>0.008728494523547587</v>
+        <v>0.008728494523547625</v>
       </c>
       <c r="F19">
-        <v>0.5251277962349262</v>
+        <v>0.06203366081069026</v>
       </c>
       <c r="G19">
-        <v>0.9110773195055606</v>
+        <v>0.6690138966255897</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.7197976712367912</v>
+        <v>0.7042081428822723</v>
       </c>
       <c r="C21">
-        <v>0.1448278261172165</v>
+        <v>0.1454521779432943</v>
       </c>
       <c r="D21">
-        <v>-2.270179201394458</v>
+        <v>-2.410973242048321</v>
       </c>
       <c r="E21">
-        <v>0.02319671240423802</v>
+        <v>0.01591001564633446</v>
       </c>
       <c r="F21">
-        <v>0.5419169913385408</v>
+        <v>0.5295316516390202</v>
       </c>
       <c r="G21">
-        <v>0.9560665116592373</v>
+        <v>0.9365051304615089</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1698,22 +1698,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.6684308085022255</v>
+        <v>0.7192560343753495</v>
       </c>
       <c r="C22">
-        <v>0.1490304016257154</v>
+        <v>0.1464888598927671</v>
       </c>
       <c r="D22">
-        <v>-2.702954471149119</v>
+        <v>-2.249576432027913</v>
       </c>
       <c r="E22">
-        <v>0.006872615941757151</v>
+        <v>0.02447584592569381</v>
       </c>
       <c r="F22">
-        <v>0.4991160674391739</v>
+        <v>0.5397491543698332</v>
       </c>
       <c r="G22">
-        <v>0.895182052638266</v>
+        <v>0.9584623501436422</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.039641338174199</v>
+        <v>1.123054848934127</v>
       </c>
       <c r="C23">
-        <v>0.1305995303374645</v>
+        <v>0.1281702033649042</v>
       </c>
       <c r="D23">
-        <v>0.2976717177488071</v>
+        <v>0.9054562835523645</v>
       </c>
       <c r="E23">
-        <v>0.7659537313636201</v>
+        <v>0.3652237097159564</v>
       </c>
       <c r="F23">
-        <v>0.8048538351220935</v>
+        <v>0.8735792151245455</v>
       </c>
       <c r="G23">
-        <v>1.342919751232443</v>
+        <v>1.443775414842762</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="O23">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="24">
@@ -1946,26 +1946,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B26">
-        <v>1.252898112060033</v>
+        <v>1.37561407920924</v>
       </c>
       <c r="C26">
-        <v>0.1528869051736091</v>
+        <v>0.2162503719905992</v>
       </c>
       <c r="D26">
-        <v>1.474680628508697</v>
+        <v>1.474680628508692</v>
       </c>
       <c r="E26">
-        <v>0.1402984264865128</v>
+        <v>0.1402984264865139</v>
       </c>
       <c r="F26">
-        <v>0.9284920407032206</v>
+        <v>0.9003761070207305</v>
       </c>
       <c r="G26">
-        <v>1.690648503582968</v>
+        <v>2.10169292605975</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2009,26 +2009,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.743142721031707</v>
+        <v>0.6318011281682795</v>
       </c>
       <c r="C27">
-        <v>0.1610798362220438</v>
+        <v>0.2317341426241931</v>
       </c>
       <c r="D27">
-        <v>-1.842981543485997</v>
+        <v>-1.981497416714027</v>
       </c>
       <c r="E27">
-        <v>0.0653317052692084</v>
+        <v>0.04753551878248338</v>
       </c>
       <c r="F27">
-        <v>0.5419519997474809</v>
+        <v>0.401169527765906</v>
       </c>
       <c r="G27">
-        <v>1.019022171852363</v>
+        <v>0.9950223980811413</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2072,26 +2072,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.6665786107828672</v>
+        <v>0.6336047252163257</v>
       </c>
       <c r="C28">
-        <v>0.1660888147037136</v>
+        <v>0.2342749899176021</v>
       </c>
       <c r="D28">
-        <v>-2.442050064486562</v>
+        <v>-1.94783907980293</v>
       </c>
       <c r="E28">
-        <v>0.01460412120347696</v>
+        <v>0.05143422106309757</v>
       </c>
       <c r="F28">
-        <v>0.4813670049740717</v>
+        <v>0.4003162082688482</v>
       </c>
       <c r="G28">
-        <v>0.9230525560786</v>
+        <v>1.002844600153793</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2135,26 +2135,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.106697648466576</v>
+        <v>1.344293408820236</v>
       </c>
       <c r="C29">
-        <v>0.1536193767568482</v>
+        <v>0.2236485633781956</v>
       </c>
       <c r="D29">
-        <v>0.6599459756383003</v>
+        <v>1.322917187304041</v>
       </c>
       <c r="E29">
-        <v>0.5092884988851243</v>
+        <v>0.1858629189553842</v>
       </c>
       <c r="F29">
-        <v>0.8189698931542552</v>
+        <v>0.8672095802630143</v>
       </c>
       <c r="G29">
-        <v>1.495512466769958</v>
+        <v>2.083838566969532</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2192,32 +2192,32 @@
         </is>
       </c>
       <c r="O29">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.732039275757748</v>
+        <v>0.6634542371052311</v>
       </c>
       <c r="C30">
-        <v>0.1434424189484625</v>
+        <v>0.1886815688612768</v>
       </c>
       <c r="D30">
-        <v>-2.174538838232616</v>
+        <v>-2.174538838232617</v>
       </c>
       <c r="E30">
-        <v>0.02966469192723988</v>
+        <v>0.02966469192723985</v>
       </c>
       <c r="F30">
-        <v>0.5526319303964091</v>
+        <v>0.4583581199769541</v>
       </c>
       <c r="G30">
-        <v>0.9696897189193073</v>
+        <v>0.9603223015990545</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2261,26 +2261,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.737055675237792</v>
+        <v>0.265533313647023</v>
       </c>
       <c r="C31">
-        <v>0.1321785620353435</v>
+        <v>0.5744852052681009</v>
       </c>
       <c r="D31">
-        <v>-2.308179495105756</v>
+        <v>-2.308179495105769</v>
       </c>
       <c r="E31">
-        <v>0.02098915514942207</v>
+        <v>0.02098915514942136</v>
       </c>
       <c r="F31">
-        <v>0.5688394378598084</v>
+        <v>0.08612243925160273</v>
       </c>
       <c r="G31">
-        <v>0.9550165340929172</v>
+        <v>0.8186941901445988</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2324,26 +2324,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B32">
-        <v>1.135032021139825</v>
+        <v>1.143243409656418</v>
       </c>
       <c r="C32">
-        <v>0.1361094439647052</v>
+        <v>0.1438556325795567</v>
       </c>
       <c r="D32">
-        <v>0.9305810038151542</v>
+        <v>0.9305810038151572</v>
       </c>
       <c r="E32">
-        <v>0.3520703445940427</v>
+        <v>0.3520703445940411</v>
       </c>
       <c r="F32">
-        <v>0.8692637020618149</v>
+        <v>0.8623599329373018</v>
       </c>
       <c r="G32">
-        <v>1.482056234439596</v>
+        <v>1.515614819059384</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2387,26 +2387,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.7090481637369385</v>
+        <v>0.6777787060090538</v>
       </c>
       <c r="C33">
-        <v>0.1519930791038372</v>
+        <v>0.1616783344642616</v>
       </c>
       <c r="D33">
-        <v>-2.262154466878073</v>
+        <v>-2.405606403140611</v>
       </c>
       <c r="E33">
-        <v>0.02368786140662093</v>
+        <v>0.01614564942851254</v>
       </c>
       <c r="F33">
-        <v>0.5263795314386425</v>
+        <v>0.4937044850136378</v>
       </c>
       <c r="G33">
-        <v>0.9551079942730019</v>
+        <v>0.9304836967535702</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,26 +2450,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.6556966637825393</v>
+        <v>0.7021982116973265</v>
       </c>
       <c r="C34">
-        <v>0.1564714453411897</v>
+        <v>0.1612660315459873</v>
       </c>
       <c r="D34">
-        <v>-2.697341989967505</v>
+        <v>-2.192275450545687</v>
       </c>
       <c r="E34">
-        <v>0.006989544700487029</v>
+        <v>0.02835962327956257</v>
       </c>
       <c r="F34">
-        <v>0.482518799037007</v>
+        <v>0.5119055335632368</v>
       </c>
       <c r="G34">
-        <v>0.8910287345355391</v>
+        <v>0.9632291432341235</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2513,26 +2513,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B35">
-        <v>1.0849483549273</v>
+        <v>1.192437893709174</v>
       </c>
       <c r="C35">
-        <v>0.1360603925578351</v>
+        <v>0.147174037352383</v>
       </c>
       <c r="D35">
-        <v>0.5992367446650183</v>
+        <v>1.19586215641883</v>
       </c>
       <c r="E35">
-        <v>0.5490150228540684</v>
+        <v>0.2317503552606103</v>
       </c>
       <c r="F35">
-        <v>0.8309870379180749</v>
+        <v>0.8936367100513127</v>
       </c>
       <c r="G35">
-        <v>1.416523819443141</v>
+        <v>1.591147850530811</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2570,32 +2570,32 @@
         </is>
       </c>
       <c r="O35">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.7366626106999866</v>
+        <v>0.732004596247286</v>
       </c>
       <c r="C36">
-        <v>0.1290747357599625</v>
+        <v>0.1317536626246772</v>
       </c>
       <c r="D36">
-        <v>-2.367816421945597</v>
+        <v>-2.367816421945605</v>
       </c>
       <c r="E36">
-        <v>0.01789341192685953</v>
+        <v>0.01789341192685913</v>
       </c>
       <c r="F36">
-        <v>0.5720052482430876</v>
+        <v>0.5654118249743659</v>
       </c>
       <c r="G36">
-        <v>0.9487182218522203</v>
+        <v>0.9476822119018204</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2639,26 +2639,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.719691598994373</v>
+        <v>0.3982514694720386</v>
       </c>
       <c r="C37">
-        <v>0.1252328551449245</v>
+        <v>0.3505227986482652</v>
       </c>
       <c r="D37">
-        <v>-2.626567070462014</v>
+        <v>-2.626567070461996</v>
       </c>
       <c r="E37">
-        <v>0.008625099274782942</v>
+        <v>0.008625099274783389</v>
       </c>
       <c r="F37">
-        <v>0.5630513882636082</v>
+        <v>0.2003511500951426</v>
       </c>
       <c r="G37">
-        <v>0.9199089256495746</v>
+        <v>0.7916312577258489</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2769,22 +2769,22 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.5274398585123711</v>
+        <v>0.5350821168779998</v>
       </c>
       <c r="C39">
-        <v>0.3610932825851848</v>
+        <v>0.3565540407465746</v>
       </c>
       <c r="D39">
-        <v>-1.771620972427586</v>
+        <v>-1.753829666502963</v>
       </c>
       <c r="E39">
-        <v>0.07645749593467256</v>
+        <v>0.07945969808316</v>
       </c>
       <c r="F39">
-        <v>0.2599020989550933</v>
+        <v>0.2660241638517467</v>
       </c>
       <c r="G39">
-        <v>1.070375366209017</v>
+        <v>1.07626641000252</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -2832,22 +2832,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.070258989417186</v>
+        <v>1.284716156379744</v>
       </c>
       <c r="C40">
-        <v>0.3840570209297802</v>
+        <v>0.3667499985953105</v>
       </c>
       <c r="D40">
-        <v>0.1767983962518523</v>
+        <v>0.6831296657944957</v>
       </c>
       <c r="E40">
-        <v>0.8596667488162214</v>
+        <v>0.494524911311205</v>
       </c>
       <c r="F40">
-        <v>0.5041722700478755</v>
+        <v>0.6260788329339103</v>
       </c>
       <c r="G40">
-        <v>2.27195022907453</v>
+        <v>2.636242459641455</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2895,22 +2895,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.419075278738362</v>
+        <v>1.288103676123797</v>
       </c>
       <c r="C41">
-        <v>0.3428642355126607</v>
+        <v>0.3352558484216197</v>
       </c>
       <c r="D41">
-        <v>1.02082810358745</v>
+        <v>0.755157947339518</v>
       </c>
       <c r="E41">
-        <v>0.3073358869701488</v>
+        <v>0.4501542174037761</v>
       </c>
       <c r="F41">
-        <v>0.7247010124077506</v>
+        <v>0.6676986899292554</v>
       </c>
       <c r="G41">
-        <v>2.778766156315668</v>
+        <v>2.484969800703726</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="O41">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="42">
@@ -3080,26 +3080,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B44">
-        <v>0.6757675583898971</v>
+        <v>0.5683120684556341</v>
       </c>
       <c r="C44">
-        <v>0.3796904507755642</v>
+        <v>0.5474709853597124</v>
       </c>
       <c r="D44">
-        <v>-1.032172681203266</v>
+        <v>-1.032172681203267</v>
       </c>
       <c r="E44">
-        <v>0.3019912303768714</v>
+        <v>0.3019912303768707</v>
       </c>
       <c r="F44">
-        <v>0.3210733364777605</v>
+        <v>0.1943473982458965</v>
       </c>
       <c r="G44">
-        <v>1.422297466310704</v>
+        <v>1.661862263490017</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3143,26 +3143,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B45">
-        <v>0.5456439284406078</v>
+        <v>0.4359502037554751</v>
       </c>
       <c r="C45">
-        <v>0.3948550661167611</v>
+        <v>0.5611174581820809</v>
       </c>
       <c r="D45">
-        <v>-1.534205113910786</v>
+        <v>-1.479596190814554</v>
       </c>
       <c r="E45">
-        <v>0.1249791999534478</v>
+        <v>0.1389810436750945</v>
       </c>
       <c r="F45">
-        <v>0.2516564612892591</v>
+        <v>0.1451485957752105</v>
       </c>
       <c r="G45">
-        <v>1.183070345656197</v>
+        <v>1.309365613490136</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3206,26 +3206,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B46">
-        <v>1.039104281629668</v>
+        <v>1.389737284694388</v>
       </c>
       <c r="C46">
-        <v>0.4153825849626987</v>
+        <v>0.5717933977337983</v>
       </c>
       <c r="D46">
-        <v>0.09234637121066402</v>
+        <v>0.5755832906894846</v>
       </c>
       <c r="E46">
-        <v>0.9264228468439376</v>
+        <v>0.5648968778858985</v>
       </c>
       <c r="F46">
-        <v>0.4603464909041911</v>
+        <v>0.4531284041955986</v>
       </c>
       <c r="G46">
-        <v>2.345489168344343</v>
+        <v>4.262301154787087</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3269,26 +3269,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B47">
-        <v>1.306518323182251</v>
+        <v>1.350902153693446</v>
       </c>
       <c r="C47">
-        <v>0.36690599994165</v>
+        <v>0.5305606552465035</v>
       </c>
       <c r="D47">
-        <v>0.7287038929729176</v>
+        <v>0.5668958455242424</v>
       </c>
       <c r="E47">
-        <v>0.4661828109633513</v>
+        <v>0.5707849469189419</v>
       </c>
       <c r="F47">
-        <v>0.6365090039290268</v>
+        <v>0.4775400994701923</v>
       </c>
       <c r="G47">
-        <v>2.681800443158062</v>
+        <v>3.821535889610674</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3326,32 +3326,32 @@
         </is>
       </c>
       <c r="O47">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="B48">
-        <v>0.8802785760547965</v>
+        <v>0.8379804784326915</v>
       </c>
       <c r="C48">
-        <v>0.2547124333714583</v>
+        <v>0.3530755952256687</v>
       </c>
       <c r="D48">
-        <v>-0.500630676795446</v>
+        <v>-0.5006306767954394</v>
       </c>
       <c r="E48">
-        <v>0.6166310686274626</v>
+        <v>0.6166310686274673</v>
       </c>
       <c r="F48">
-        <v>0.5343287174138406</v>
+        <v>0.4194646915059921</v>
       </c>
       <c r="G48">
-        <v>1.450212848771336</v>
+        <v>1.674065294299631</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3395,26 +3395,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="B49">
-        <v>0.917090558347287</v>
+        <v>0.6753174599746511</v>
       </c>
       <c r="C49">
-        <v>0.3089912859169747</v>
+        <v>1.401534015979498</v>
       </c>
       <c r="D49">
-        <v>-0.2801019333971893</v>
+        <v>-0.2801019333970852</v>
       </c>
       <c r="E49">
-        <v>0.7793993014194779</v>
+        <v>0.7793993014195577</v>
       </c>
       <c r="F49">
-        <v>0.5004934093115689</v>
+        <v>0.04330320700112499</v>
       </c>
       <c r="G49">
-        <v>1.680451883205843</v>
+        <v>10.53163733888732</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3458,26 +3458,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B50">
-        <v>0.6887402993933146</v>
+        <v>0.5889634182585791</v>
       </c>
       <c r="C50">
-        <v>0.3476475443737874</v>
+        <v>0.4935532129423276</v>
       </c>
       <c r="D50">
-        <v>-1.072612216062982</v>
+        <v>-1.072612216062983</v>
       </c>
       <c r="E50">
-        <v>0.2834451413970351</v>
+        <v>0.2834451413970341</v>
       </c>
       <c r="F50">
-        <v>0.3484475127140894</v>
+        <v>0.2238592601933843</v>
       </c>
       <c r="G50">
-        <v>1.361361991978461</v>
+        <v>1.549535666950628</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3521,26 +3521,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B51">
-        <v>0.5307732660588896</v>
+        <v>0.4124109239039981</v>
       </c>
       <c r="C51">
-        <v>0.3593246698092418</v>
+        <v>0.5116168909800767</v>
       </c>
       <c r="D51">
-        <v>-1.762807834774735</v>
+        <v>-1.731246669515548</v>
       </c>
       <c r="E51">
-        <v>0.07793290556585193</v>
+        <v>0.08340777878750036</v>
       </c>
       <c r="F51">
-        <v>0.2624528703088841</v>
+        <v>0.15130074733418</v>
       </c>
       <c r="G51">
-        <v>1.073412760284392</v>
+        <v>1.124137012883917</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3584,26 +3584,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.054873605649577</v>
+        <v>1.416175817934785</v>
       </c>
       <c r="C52">
-        <v>0.3844283498766234</v>
+        <v>0.5309725013720765</v>
       </c>
       <c r="D52">
-        <v>0.1389620580700745</v>
+        <v>0.6553261268195437</v>
       </c>
       <c r="E52">
-        <v>0.8894801313602037</v>
+        <v>0.5122578027490079</v>
       </c>
       <c r="F52">
-        <v>0.496563074292787</v>
+        <v>0.5002102211112219</v>
       </c>
       <c r="G52">
-        <v>2.24092040166488</v>
+        <v>4.009422164241062</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3647,26 +3647,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.374187839977673</v>
+        <v>1.391370490042604</v>
       </c>
       <c r="C53">
-        <v>0.3327809076828068</v>
+        <v>0.4842426620265166</v>
       </c>
       <c r="D53">
-        <v>0.9551716683147776</v>
+        <v>0.6820737852309176</v>
       </c>
       <c r="E53">
-        <v>0.3394908907313913</v>
+        <v>0.4951922958634699</v>
       </c>
       <c r="F53">
-        <v>0.7157848120476307</v>
+        <v>0.538585537014128</v>
       </c>
       <c r="G53">
-        <v>2.638212194165474</v>
+        <v>3.59443710890182</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3704,32 +3704,32 @@
         </is>
       </c>
       <c r="O53">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="B54">
-        <v>0.8831489895114666</v>
+        <v>0.8405308311755956</v>
       </c>
       <c r="C54">
-        <v>0.2243434489331108</v>
+        <v>0.3136398351866477</v>
       </c>
       <c r="D54">
-        <v>-0.5538889687175316</v>
+        <v>-0.5538889687174827</v>
       </c>
       <c r="E54">
-        <v>0.5796548350988817</v>
+        <v>0.579654835098915</v>
       </c>
       <c r="F54">
-        <v>0.5689478838141113</v>
+        <v>0.4545513338657995</v>
       </c>
       <c r="G54">
-        <v>1.370867455286912</v>
+        <v>1.55426246832953</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3773,26 +3773,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="B55">
-        <v>0.8961394225478746</v>
+        <v>0.6229408715781418</v>
       </c>
       <c r="C55">
-        <v>0.2927909169382431</v>
+        <v>1.263723654124917</v>
       </c>
       <c r="D55">
-        <v>-0.374530992071173</v>
+        <v>-0.3745309920711696</v>
       </c>
       <c r="E55">
-        <v>0.7080093032920046</v>
+        <v>0.7080093032920072</v>
       </c>
       <c r="F55">
-        <v>0.5048373782727211</v>
+        <v>0.0523315142542289</v>
       </c>
       <c r="G55">
-        <v>1.590741690704624</v>
+        <v>7.415327742999076</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3903,22 +3903,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.6099260404732069</v>
+        <v>0.6099193629937284</v>
       </c>
       <c r="C57">
-        <v>0.2648870982656472</v>
+        <v>0.2629983983417432</v>
       </c>
       <c r="D57">
-        <v>-1.866521916426517</v>
+        <v>-1.879967807727794</v>
       </c>
       <c r="E57">
-        <v>0.06196838069834797</v>
+        <v>0.06011246544762526</v>
       </c>
       <c r="F57">
-        <v>0.3629149582847874</v>
+        <v>0.3642568926946917</v>
       </c>
       <c r="G57">
-        <v>1.02506046211355</v>
+        <v>1.021261743608171</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -3966,22 +3966,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.7966407131513356</v>
+        <v>0.8789560712136923</v>
       </c>
       <c r="C58">
-        <v>0.273075272605059</v>
+        <v>0.2623163131108395</v>
       </c>
       <c r="D58">
-        <v>-0.8325598239664559</v>
+        <v>-0.491850304244652</v>
       </c>
       <c r="E58">
-        <v>0.4050930254270043</v>
+        <v>0.6228251718875212</v>
       </c>
       <c r="F58">
-        <v>0.4664664404651016</v>
+        <v>0.5256336011815496</v>
       </c>
       <c r="G58">
-        <v>1.360518937262644</v>
+        <v>1.46977623459915</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4029,22 +4029,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.917201983216688</v>
+        <v>0.8720890212556835</v>
       </c>
       <c r="C59">
-        <v>0.2292503871196729</v>
+        <v>0.2280006315348401</v>
       </c>
       <c r="D59">
-        <v>-0.3770007406989957</v>
+        <v>-0.6002780376814986</v>
       </c>
       <c r="E59">
-        <v>0.7061730544621327</v>
+        <v>0.5483209529656095</v>
       </c>
       <c r="F59">
-        <v>0.5852301630914087</v>
+        <v>0.5578100437480855</v>
       </c>
       <c r="G59">
-        <v>1.437484824043881</v>
+        <v>1.363437732107537</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="O59">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="60">
@@ -4214,26 +4214,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B62">
-        <v>0.7087907459944196</v>
+        <v>0.6145620514898293</v>
       </c>
       <c r="C62">
-        <v>0.3326090417379862</v>
+        <v>0.4704577473237525</v>
       </c>
       <c r="D62">
-        <v>-1.034833370298402</v>
+        <v>-1.034833370298393</v>
       </c>
       <c r="E62">
-        <v>0.3007467357032289</v>
+        <v>0.3007467357032332</v>
       </c>
       <c r="F62">
-        <v>0.369318199083896</v>
+        <v>0.2444057274433336</v>
       </c>
       <c r="G62">
-        <v>1.360302099526923</v>
+        <v>1.545325958938322</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4277,26 +4277,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B63">
-        <v>0.6555848243635065</v>
+        <v>0.5595925708447244</v>
       </c>
       <c r="C63">
-        <v>0.3467822782392748</v>
+        <v>0.4897476519221335</v>
       </c>
       <c r="D63">
-        <v>-1.217558123877699</v>
+        <v>-1.18539886782894</v>
       </c>
       <c r="E63">
-        <v>0.2233919360119173</v>
+        <v>0.2358597791675618</v>
       </c>
       <c r="F63">
-        <v>0.3322364529405937</v>
+        <v>0.2142880649178205</v>
       </c>
       <c r="G63">
-        <v>1.293631262107712</v>
+        <v>1.461321914800521</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4340,26 +4340,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.04879847485628</v>
+        <v>1.332479929090431</v>
       </c>
       <c r="C64">
-        <v>0.3611669403681194</v>
+        <v>0.4887568574729155</v>
       </c>
       <c r="D64">
-        <v>0.1319201564738596</v>
+        <v>0.5872895898223335</v>
       </c>
       <c r="E64">
-        <v>0.8950474454029796</v>
+        <v>0.5570092315142178</v>
       </c>
       <c r="F64">
-        <v>0.5167329910293118</v>
+        <v>0.5112461902453284</v>
       </c>
       <c r="G64">
-        <v>2.128716880781592</v>
+        <v>3.472891916469523</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4403,26 +4403,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B65">
-        <v>1.13678792147405</v>
+        <v>1.063306963276457</v>
       </c>
       <c r="C65">
-        <v>0.3156610524013379</v>
+        <v>0.4567318745702157</v>
       </c>
       <c r="D65">
-        <v>0.4061529661203701</v>
+        <v>0.1343979516480329</v>
       </c>
       <c r="E65">
-        <v>0.6846302102912227</v>
+        <v>0.8930879012889352</v>
       </c>
       <c r="F65">
-        <v>0.6123338606309202</v>
+        <v>0.4343979644098128</v>
       </c>
       <c r="G65">
-        <v>2.110428414129801</v>
+        <v>2.602732495968991</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4460,32 +4460,32 @@
         </is>
       </c>
       <c r="O65">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="B66">
-        <v>0.8771528009287609</v>
+        <v>0.8416319566495764</v>
       </c>
       <c r="C66">
-        <v>0.247119381147121</v>
+        <v>0.3250563736492688</v>
       </c>
       <c r="D66">
-        <v>-0.5304078934980518</v>
+        <v>-0.5304078934980661</v>
       </c>
       <c r="E66">
-        <v>0.5958291543454696</v>
+        <v>0.5958291543454597</v>
       </c>
       <c r="F66">
-        <v>0.5404143292035267</v>
+        <v>0.4450755429820487</v>
       </c>
       <c r="G66">
-        <v>1.423716941982502</v>
+        <v>1.591514882412589</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4529,26 +4529,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="B67">
-        <v>0.9523306314556079</v>
+        <v>0.8087338310275783</v>
       </c>
       <c r="C67">
-        <v>0.2160501432198479</v>
+        <v>0.9390146856240488</v>
       </c>
       <c r="D67">
-        <v>-0.2260725302425004</v>
+        <v>-0.2260725302425316</v>
       </c>
       <c r="E67">
-        <v>0.821145009221437</v>
+        <v>0.8211450092214128</v>
       </c>
       <c r="F67">
-        <v>0.6235704668137363</v>
+        <v>0.1283851702757511</v>
       </c>
       <c r="G67">
-        <v>1.45442043822698</v>
+        <v>5.094438929696837</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4592,26 +4592,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B68">
-        <v>0.6647179760462011</v>
+        <v>0.6494466165243009</v>
       </c>
       <c r="C68">
-        <v>0.2702247828510279</v>
+        <v>0.2856036726282435</v>
       </c>
       <c r="D68">
-        <v>-1.511306328541918</v>
+        <v>-1.511306328541989</v>
       </c>
       <c r="E68">
-        <v>0.130710422313406</v>
+        <v>0.1307104223133879</v>
       </c>
       <c r="F68">
-        <v>0.3914007661468231</v>
+        <v>0.3710540461235651</v>
       </c>
       <c r="G68">
-        <v>1.128894028565111</v>
+        <v>1.136710169640367</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4655,26 +4655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B69">
-        <v>0.5744532123595267</v>
+        <v>0.5581575723427373</v>
       </c>
       <c r="C69">
-        <v>0.2933727167015731</v>
+        <v>0.3083323849522541</v>
       </c>
       <c r="D69">
-        <v>-1.889530259901901</v>
+        <v>-1.891186256169714</v>
       </c>
       <c r="E69">
-        <v>0.05882081203999408</v>
+        <v>0.05859948534878703</v>
       </c>
       <c r="F69">
-        <v>0.3232476328202015</v>
+        <v>0.3050027949862132</v>
       </c>
       <c r="G69">
-        <v>1.020878297889136</v>
+        <v>1.02143285466489</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4718,26 +4718,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B70">
-        <v>0.7911611455706631</v>
+        <v>0.9045513476168043</v>
       </c>
       <c r="C70">
-        <v>0.3026114847297814</v>
+        <v>0.3033349552392349</v>
       </c>
       <c r="D70">
-        <v>-0.7741068000635574</v>
+        <v>-0.330711001034229</v>
       </c>
       <c r="E70">
-        <v>0.4388676365212664</v>
+        <v>0.7408627918411497</v>
       </c>
       <c r="F70">
-        <v>0.4372014441590365</v>
+        <v>0.4991534106950636</v>
       </c>
       <c r="G70">
-        <v>1.431687764583397</v>
+        <v>1.639201742278045</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4781,26 +4781,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B71">
-        <v>1.020003542393396</v>
+        <v>0.9498768022533964</v>
       </c>
       <c r="C71">
-        <v>0.2475251288848368</v>
+        <v>0.2721732369756755</v>
       </c>
       <c r="D71">
-        <v>0.08001652322769168</v>
+        <v>-0.1889347579023468</v>
       </c>
       <c r="E71">
-        <v>0.9362241144726239</v>
+        <v>0.8501439512811031</v>
       </c>
       <c r="F71">
-        <v>0.6279251938652233</v>
+        <v>0.5571767710463185</v>
       </c>
       <c r="G71">
-        <v>1.656896771557771</v>
+        <v>1.619353114389135</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4838,32 +4838,32 @@
         </is>
       </c>
       <c r="O71">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="B72">
-        <v>0.7785089448783533</v>
+        <v>0.7744739227921351</v>
       </c>
       <c r="C72">
-        <v>0.2089366998447418</v>
+        <v>0.213273149847474</v>
       </c>
       <c r="D72">
-        <v>-1.198328479733059</v>
+        <v>-1.198328479733077</v>
       </c>
       <c r="E72">
-        <v>0.2307891634914588</v>
+        <v>0.2307891634914519</v>
       </c>
       <c r="F72">
-        <v>0.5169117038600427</v>
+        <v>0.5098804553599308</v>
       </c>
       <c r="G72">
-        <v>1.172494591880446</v>
+        <v>1.17637350241563</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4907,26 +4907,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="B73">
-        <v>0.7996940544129655</v>
+        <v>0.5349177091086501</v>
       </c>
       <c r="C73">
-        <v>0.1736782292902798</v>
+        <v>0.4861198678625784</v>
       </c>
       <c r="D73">
-        <v>-1.287012525157484</v>
+        <v>-1.287012525157442</v>
       </c>
       <c r="E73">
-        <v>0.1980899225406911</v>
+        <v>0.1980899225407056</v>
       </c>
       <c r="F73">
-        <v>0.568969112163801</v>
+        <v>0.2063008390357486</v>
       </c>
       <c r="G73">
-        <v>1.123981191582396</v>
+        <v>1.386988811366218</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4974,22 +4974,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.912904521645401</v>
+        <v>1.075074466147093</v>
       </c>
       <c r="C74">
-        <v>0.3012301957988095</v>
+        <v>0.3151826528470333</v>
       </c>
       <c r="D74">
-        <v>-0.3025061286604742</v>
+        <v>0.2296761238638047</v>
       </c>
       <c r="E74">
-        <v>0.7622662621843282</v>
+        <v>0.8183434493594974</v>
       </c>
       <c r="F74">
-        <v>0.5058453366621194</v>
+        <v>0.5796349801581735</v>
       </c>
       <c r="G74">
-        <v>1.647528612480392</v>
+        <v>1.993987849812068</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         </is>
       </c>
       <c r="O74">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="75">
@@ -5037,22 +5037,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.6796946010992231</v>
+        <v>0.5752138398579068</v>
       </c>
       <c r="C75">
-        <v>0.3160195179594644</v>
+        <v>0.3155852720862689</v>
       </c>
       <c r="D75">
-        <v>-1.221796996016164</v>
+        <v>-1.752342269523004</v>
       </c>
       <c r="E75">
-        <v>0.2217844048438847</v>
+        <v>0.07971497183621183</v>
       </c>
       <c r="F75">
-        <v>0.3658621809277326</v>
+        <v>0.3098864994796243</v>
       </c>
       <c r="G75">
-        <v>1.262728904069716</v>
+        <v>1.067716606304861</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="O75">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="76">
@@ -5100,22 +5100,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.6656324459310071</v>
+        <v>0.7671082748732443</v>
       </c>
       <c r="C76">
-        <v>0.3196547870643439</v>
+        <v>0.3098879122853718</v>
       </c>
       <c r="D76">
-        <v>-1.273303764694639</v>
+        <v>-0.8555587693111125</v>
       </c>
       <c r="E76">
-        <v>0.2029102713363233</v>
+        <v>0.3922418841645862</v>
       </c>
       <c r="F76">
-        <v>0.3557491206257032</v>
+        <v>0.4179069544760954</v>
       </c>
       <c r="G76">
-        <v>1.245446657174626</v>
+        <v>1.408100772375792</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="O76">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="77">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.8727617687127599</v>
+        <v>0.8278661612972958</v>
       </c>
       <c r="C77">
-        <v>0.2890239080686176</v>
+        <v>0.2927860855808655</v>
       </c>
       <c r="D77">
-        <v>-0.4708698645905449</v>
+        <v>-0.6451938391563485</v>
       </c>
       <c r="E77">
-        <v>0.6377336693444851</v>
+        <v>0.5188015781609266</v>
       </c>
       <c r="F77">
-        <v>0.4953111644090948</v>
+        <v>0.4663802635008185</v>
       </c>
       <c r="G77">
-        <v>1.537847639342729</v>
+        <v>1.469535558551605</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5216,32 +5216,32 @@
         </is>
       </c>
       <c r="O77">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B78">
-        <v>0.7249568321092293</v>
+        <v>0.8703927382431438</v>
       </c>
       <c r="C78">
-        <v>0.3770314060358479</v>
+        <v>0.5461934346132492</v>
       </c>
       <c r="D78">
-        <v>-0.8530938342782917</v>
+        <v>-0.2541420989885124</v>
       </c>
       <c r="E78">
-        <v>0.3936072703594951</v>
+        <v>0.7993857804980095</v>
       </c>
       <c r="F78">
-        <v>0.3462441403885946</v>
+        <v>0.2983970769750418</v>
       </c>
       <c r="G78">
-        <v>1.51789545905962</v>
+        <v>2.538843632338138</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5279,32 +5279,32 @@
         </is>
       </c>
       <c r="O78">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B79">
-        <v>0.5372444627162813</v>
+        <v>0.3138360762250854</v>
       </c>
       <c r="C79">
-        <v>0.362683941039785</v>
+        <v>0.5460602210320107</v>
       </c>
       <c r="D79">
-        <v>-1.713067439513394</v>
+        <v>-2.122264971870567</v>
       </c>
       <c r="E79">
-        <v>0.08670013337847154</v>
+        <v>0.03381549322298054</v>
       </c>
       <c r="F79">
-        <v>0.2639093746952281</v>
+        <v>0.1076206380464336</v>
       </c>
       <c r="G79">
-        <v>1.093676998221938</v>
+        <v>0.9151876863790949</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5342,32 +5342,32 @@
         </is>
       </c>
       <c r="O79">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B80">
-        <v>0.5388630957001072</v>
+        <v>0.4790350051826305</v>
       </c>
       <c r="C80">
-        <v>0.3746583873468798</v>
+        <v>0.5731115012047083</v>
       </c>
       <c r="D80">
-        <v>-1.65028665595884</v>
+        <v>-1.284185717754972</v>
       </c>
       <c r="E80">
-        <v>0.09888432023130592</v>
+        <v>0.1990769812711287</v>
       </c>
       <c r="F80">
-        <v>0.2585643492128143</v>
+        <v>0.1557879477050247</v>
       </c>
       <c r="G80">
-        <v>1.123021935512493</v>
+        <v>1.472992869928675</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5405,32 +5405,32 @@
         </is>
       </c>
       <c r="O80">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B81">
-        <v>0.650058421673132</v>
+        <v>0.5290043433306257</v>
       </c>
       <c r="C81">
-        <v>0.3600550983340789</v>
+        <v>0.520390906114967</v>
       </c>
       <c r="D81">
-        <v>-1.196186479866555</v>
+        <v>-1.223615995630021</v>
       </c>
       <c r="E81">
-        <v>0.2316237957195537</v>
+        <v>0.2210971225648322</v>
       </c>
       <c r="F81">
-        <v>0.3209762757773484</v>
+        <v>0.1907663171185499</v>
       </c>
       <c r="G81">
-        <v>1.31653328759192</v>
+        <v>1.466954960863239</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5468,32 +5468,32 @@
         </is>
       </c>
       <c r="O81">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B82">
-        <v>0.7775371493567511</v>
+        <v>0.8890883111039378</v>
       </c>
       <c r="C82">
-        <v>0.3145163806816396</v>
+        <v>0.4507184902358971</v>
       </c>
       <c r="D82">
-        <v>-0.8000341826448374</v>
+        <v>-0.2608251344772243</v>
       </c>
       <c r="E82">
-        <v>0.4236909925906668</v>
+        <v>0.7942273606471306</v>
       </c>
       <c r="F82">
-        <v>0.4197631588623429</v>
+        <v>0.3675298574543157</v>
       </c>
       <c r="G82">
-        <v>1.440250307502768</v>
+        <v>2.150785871974795</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5531,32 +5531,32 @@
         </is>
       </c>
       <c r="O82">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B83">
-        <v>0.5909444451238096</v>
+        <v>0.3655410807506998</v>
       </c>
       <c r="C83">
-        <v>0.3114600870854067</v>
+        <v>0.4610426632266808</v>
       </c>
       <c r="D83">
-        <v>-1.688926733436522</v>
+        <v>-2.182827513250576</v>
       </c>
       <c r="E83">
-        <v>0.09123347141436584</v>
+        <v>0.02904851472464896</v>
       </c>
       <c r="F83">
-        <v>0.3209455421761097</v>
+        <v>0.1480798497555395</v>
       </c>
       <c r="G83">
-        <v>1.088082840642994</v>
+        <v>0.902352899040479</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5594,32 +5594,32 @@
         </is>
       </c>
       <c r="O83">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B84">
-        <v>0.5797658247415464</v>
+        <v>0.5225471270906458</v>
       </c>
       <c r="C84">
-        <v>0.3207435233009298</v>
+        <v>0.4746154834294857</v>
       </c>
       <c r="D84">
-        <v>-1.699585393981542</v>
+        <v>-1.367507227391505</v>
       </c>
       <c r="E84">
-        <v>0.08920893963199679</v>
+        <v>0.1714663734459378</v>
       </c>
       <c r="F84">
-        <v>0.3091969701356375</v>
+        <v>0.2061256472858269</v>
       </c>
       <c r="G84">
-        <v>1.087101246143498</v>
+        <v>1.324704148300631</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5657,32 +5657,32 @@
         </is>
       </c>
       <c r="O84">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B85">
-        <v>0.7350768556732585</v>
+        <v>0.6157807813097967</v>
       </c>
       <c r="C85">
-        <v>0.301812598935573</v>
+        <v>0.4369321038536699</v>
       </c>
       <c r="D85">
-        <v>-1.019772603196555</v>
+        <v>-1.109701596672877</v>
       </c>
       <c r="E85">
-        <v>0.3078363193484421</v>
+        <v>0.2671276346463584</v>
       </c>
       <c r="F85">
-        <v>0.4068453896634656</v>
+        <v>0.2615223735766521</v>
       </c>
       <c r="G85">
-        <v>1.328116275800597</v>
+        <v>1.449917899737035</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="O85">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="86">
@@ -5730,22 +5730,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>0.978619735445479</v>
+        <v>1.132459826610417</v>
       </c>
       <c r="C86">
-        <v>0.2288548899051759</v>
+        <v>0.255776301188589</v>
       </c>
       <c r="D86">
-        <v>-0.09443596909692299</v>
+        <v>0.4863316264099917</v>
       </c>
       <c r="E86">
-        <v>0.9247628442578968</v>
+        <v>0.6267320593228322</v>
       </c>
       <c r="F86">
-        <v>0.6249026038614365</v>
+        <v>0.6859707889459477</v>
       </c>
       <c r="G86">
-        <v>1.532553362212802</v>
+        <v>1.869562493844835</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="O86">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="87">
@@ -5793,22 +5793,22 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.7528695811000077</v>
+        <v>0.6349402734790716</v>
       </c>
       <c r="C87">
-        <v>0.27696044194407</v>
+        <v>0.2714991186426453</v>
       </c>
       <c r="D87">
-        <v>-1.024923499041186</v>
+        <v>-1.673023265406127</v>
       </c>
       <c r="E87">
-        <v>0.3053992857082931</v>
+        <v>0.09432271606936815</v>
       </c>
       <c r="F87">
-        <v>0.4374924823176771</v>
+        <v>0.3729343663310408</v>
       </c>
       <c r="G87">
-        <v>1.295593933735576</v>
+        <v>1.081019040567092</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O87">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="88">
@@ -5856,22 +5856,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>0.7111740323265375</v>
+        <v>0.8313293066379862</v>
       </c>
       <c r="C88">
-        <v>0.2798127971036494</v>
+        <v>0.2606285847317802</v>
       </c>
       <c r="D88">
-        <v>-1.218093351890305</v>
+        <v>-0.7087836711053932</v>
       </c>
       <c r="E88">
-        <v>0.2231884999553661</v>
+        <v>0.4784587323462542</v>
       </c>
       <c r="F88">
-        <v>0.4109592932154788</v>
+        <v>0.4987990725716105</v>
       </c>
       <c r="G88">
-        <v>1.230702195096478</v>
+        <v>1.385544709440043</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="O88">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="89">
@@ -5919,22 +5919,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>0.9548768036556994</v>
+        <v>0.8782383425747295</v>
       </c>
       <c r="C89">
-        <v>0.2224341376332043</v>
+        <v>0.2410708126121319</v>
       </c>
       <c r="D89">
-        <v>-0.2075803144326174</v>
+        <v>-0.5385855715493466</v>
       </c>
       <c r="E89">
-        <v>0.8355566763626587</v>
+        <v>0.5901728455005131</v>
       </c>
       <c r="F89">
-        <v>0.6174631755940339</v>
+        <v>0.5475358325582234</v>
       </c>
       <c r="G89">
-        <v>1.47667058733103</v>
+        <v>1.40867965255295</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -5972,32 +5972,32 @@
         </is>
       </c>
       <c r="O89">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B90">
-        <v>0.9513733951800583</v>
+        <v>1.221553860905619</v>
       </c>
       <c r="C90">
-        <v>0.2996146679379439</v>
+        <v>0.4489068486616338</v>
       </c>
       <c r="D90">
-        <v>-0.1663758973542482</v>
+        <v>0.4458022982038808</v>
       </c>
       <c r="E90">
-        <v>0.8678611407105272</v>
+        <v>0.6557400615628214</v>
       </c>
       <c r="F90">
-        <v>0.5288329837693423</v>
+        <v>0.5067601060501465</v>
       </c>
       <c r="G90">
-        <v>1.711525878369206</v>
+        <v>2.944576373077332</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -6035,32 +6035,32 @@
         </is>
       </c>
       <c r="O90">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B91">
-        <v>0.6771273182363025</v>
+        <v>0.4308995201532797</v>
       </c>
       <c r="C91">
-        <v>0.3166410409855048</v>
+        <v>0.4605996814001371</v>
       </c>
       <c r="D91">
-        <v>-1.231350049097952</v>
+        <v>-1.827791859068676</v>
       </c>
       <c r="E91">
-        <v>0.2181919705091955</v>
+        <v>0.06758079548798651</v>
       </c>
       <c r="F91">
-        <v>0.3640365523937779</v>
+        <v>0.17470802364066</v>
       </c>
       <c r="G91">
-        <v>1.25949276820402</v>
+        <v>1.062769714859933</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -6098,32 +6098,32 @@
         </is>
       </c>
       <c r="O91">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B92">
-        <v>0.6891484441708046</v>
+        <v>0.7328140779704971</v>
       </c>
       <c r="C92">
-        <v>0.320786755985505</v>
+        <v>0.4531570907664245</v>
       </c>
       <c r="D92">
-        <v>-1.1605796545637</v>
+        <v>-0.6859944618249387</v>
       </c>
       <c r="E92">
-        <v>0.2458128832734383</v>
+        <v>0.4927166007638971</v>
       </c>
       <c r="F92">
-        <v>0.3675010618670408</v>
+        <v>0.3014850553082435</v>
       </c>
       <c r="G92">
-        <v>1.292310764192744</v>
+        <v>1.781237455776025</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6161,32 +6161,32 @@
         </is>
       </c>
       <c r="O92">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B93">
-        <v>0.8483898595390889</v>
+        <v>0.6897938919061797</v>
       </c>
       <c r="C93">
-        <v>0.2846067735238187</v>
+        <v>0.4308408968512673</v>
       </c>
       <c r="D93">
-        <v>-0.5776918334729255</v>
+        <v>-0.8619479629467869</v>
       </c>
       <c r="E93">
-        <v>0.5634721936937157</v>
+        <v>0.3887161538448774</v>
       </c>
       <c r="F93">
-        <v>0.4856660483048088</v>
+        <v>0.296474201546684</v>
       </c>
       <c r="G93">
-        <v>1.482017028534437</v>
+        <v>1.604914056025041</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6224,32 +6224,32 @@
         </is>
       </c>
       <c r="O93">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B94">
-        <v>0.8891600778064451</v>
+        <v>1.02046861220264</v>
       </c>
       <c r="C94">
-        <v>0.2347118335446893</v>
+        <v>0.2699883155517628</v>
       </c>
       <c r="D94">
-        <v>-0.5005201181367041</v>
+        <v>0.0750474904074325</v>
       </c>
       <c r="E94">
-        <v>0.616708893961708</v>
+        <v>0.9401769265197791</v>
       </c>
       <c r="F94">
-        <v>0.5612972057922191</v>
+        <v>0.6011532235881218</v>
       </c>
       <c r="G94">
-        <v>1.408533012112357</v>
+        <v>1.732264167652978</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6287,32 +6287,32 @@
         </is>
       </c>
       <c r="O94">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B95">
-        <v>0.7380668640775955</v>
+        <v>0.6029583592116198</v>
       </c>
       <c r="C95">
-        <v>0.2679607073779011</v>
+        <v>0.2832062279022103</v>
       </c>
       <c r="D95">
-        <v>-1.133452959303698</v>
+        <v>-1.786355986662534</v>
       </c>
       <c r="E95">
-        <v>0.2570240849497257</v>
+        <v>0.0740416371981641</v>
       </c>
       <c r="F95">
-        <v>0.4365230090519009</v>
+        <v>0.3461160527608606</v>
       </c>
       <c r="G95">
-        <v>1.247912903909649</v>
+        <v>1.050395611654452</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6350,32 +6350,32 @@
         </is>
       </c>
       <c r="O95">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B96">
-        <v>0.6395478880360784</v>
+        <v>0.7241013184501577</v>
       </c>
       <c r="C96">
-        <v>0.2715455206167304</v>
+        <v>0.2729791524778999</v>
       </c>
       <c r="D96">
-        <v>-1.646109927324576</v>
+        <v>-1.182595633572768</v>
       </c>
       <c r="E96">
-        <v>0.09974112894276953</v>
+        <v>0.2369694438437516</v>
       </c>
       <c r="F96">
-        <v>0.3756065031452452</v>
+        <v>0.4240714765606303</v>
       </c>
       <c r="G96">
-        <v>1.08896277797736</v>
+        <v>1.236401758575463</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6413,32 +6413,32 @@
         </is>
       </c>
       <c r="O96">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B97">
-        <v>0.9379700417556951</v>
+        <v>0.8712642264864066</v>
       </c>
       <c r="C97">
-        <v>0.2211171768948511</v>
+        <v>0.2577344618495573</v>
       </c>
       <c r="D97">
-        <v>-0.2896078441846743</v>
+        <v>-0.5346975613175242</v>
       </c>
       <c r="E97">
-        <v>0.7721162652812485</v>
+        <v>0.5928590080987074</v>
       </c>
       <c r="F97">
-        <v>0.608098154337982</v>
+        <v>0.5257338141841839</v>
       </c>
       <c r="G97">
-        <v>1.446785840336876</v>
+        <v>1.443889154310731</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="O97">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="98">
@@ -6486,22 +6486,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.4879913108153324</v>
+        <v>0.5555706053795282</v>
       </c>
       <c r="C98">
-        <v>0.608516931473176</v>
+        <v>0.6097814286279767</v>
       </c>
       <c r="D98">
-        <v>-1.179026649688917</v>
+        <v>-0.9638856613071354</v>
       </c>
       <c r="E98">
-        <v>0.2383875642105824</v>
+        <v>0.3351032533923238</v>
       </c>
       <c r="F98">
-        <v>0.1480612930585082</v>
+        <v>0.1681482557315486</v>
       </c>
       <c r="G98">
-        <v>1.608357691008171</v>
+        <v>1.835634251565202</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="O98">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="99">
@@ -6549,22 +6549,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.4104579670805152</v>
+        <v>0.3039676796040889</v>
       </c>
       <c r="C99">
-        <v>0.4959614539579715</v>
+        <v>0.5589782810471452</v>
       </c>
       <c r="D99">
-        <v>-1.795465640868789</v>
+        <v>-2.130375974696151</v>
       </c>
       <c r="E99">
-        <v>0.07257954231131102</v>
+        <v>0.03314058567567348</v>
       </c>
       <c r="F99">
-        <v>0.1552764290462134</v>
+        <v>0.1016305399128579</v>
       </c>
       <c r="G99">
-        <v>1.085005263031439</v>
+        <v>0.9091396181021808</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         </is>
       </c>
       <c r="O99">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="100">
@@ -6612,22 +6612,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.71935476208719</v>
+        <v>0.7364420929228281</v>
       </c>
       <c r="C100">
-        <v>0.5742571358670966</v>
+        <v>0.643540646823513</v>
       </c>
       <c r="D100">
-        <v>-0.5736117358598731</v>
+        <v>-0.4753773865893974</v>
       </c>
       <c r="E100">
-        <v>0.5662305683341795</v>
+        <v>0.6345180095374666</v>
       </c>
       <c r="F100">
-        <v>0.2334181177784201</v>
+        <v>0.2086199379400663</v>
       </c>
       <c r="G100">
-        <v>2.216928482941262</v>
+        <v>2.599688992259045</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="O100">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="101">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.6206420104559134</v>
+        <v>0.5395062720874311</v>
       </c>
       <c r="C101">
-        <v>0.5586364291287933</v>
+        <v>0.536632406970145</v>
       </c>
       <c r="D101">
-        <v>-0.8538663271792247</v>
+        <v>-1.149950805420811</v>
       </c>
       <c r="E101">
-        <v>0.3931790588153476</v>
+        <v>0.250164133743608</v>
       </c>
       <c r="F101">
-        <v>0.2076485861973945</v>
+        <v>0.1884578208486342</v>
       </c>
       <c r="G101">
-        <v>1.855040345791631</v>
+        <v>1.544467702698615</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -6728,32 +6728,32 @@
         </is>
       </c>
       <c r="O101">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
       <c r="B102">
-        <v>0.2923826097157123</v>
+        <v>0.2213860210850722</v>
       </c>
       <c r="C102">
-        <v>0.6817976636160101</v>
+        <v>0.9939807221485749</v>
       </c>
       <c r="D102">
-        <v>-1.80360258298599</v>
+        <v>-1.516978514605464</v>
       </c>
       <c r="E102">
-        <v>0.07129363086912996</v>
+        <v>0.1292721086843879</v>
       </c>
       <c r="F102">
-        <v>0.07684300054372453</v>
+        <v>0.03155529686377445</v>
       </c>
       <c r="G102">
-        <v>1.11249677731581</v>
+        <v>1.553202638006098</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6791,32 +6791,32 @@
         </is>
       </c>
       <c r="O102">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B103">
-        <v>0.327452345509116</v>
+        <v>0.1260933904981573</v>
       </c>
       <c r="C103">
-        <v>0.5587399105255511</v>
+        <v>0.9357617937692524</v>
       </c>
       <c r="D103">
-        <v>-1.998090208627039</v>
+        <v>-2.212884161265932</v>
       </c>
       <c r="E103">
-        <v>0.04570688107952407</v>
+        <v>0.02690563293709675</v>
       </c>
       <c r="F103">
-        <v>0.1095337184862474</v>
+        <v>0.02014514694406275</v>
       </c>
       <c r="G103">
-        <v>0.9789226556102372</v>
+        <v>0.7892493001649098</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6854,32 +6854,32 @@
         </is>
       </c>
       <c r="O103">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B104">
-        <v>0.495553477948236</v>
+        <v>0.3264204147689848</v>
       </c>
       <c r="C104">
-        <v>0.6229896654269339</v>
+        <v>1.056213533351837</v>
       </c>
       <c r="D104">
-        <v>-1.126952889841341</v>
+        <v>-1.059983684404279</v>
       </c>
       <c r="E104">
-        <v>0.2597623996920659</v>
+        <v>0.2891520219971284</v>
       </c>
       <c r="F104">
-        <v>0.1461506542643385</v>
+        <v>0.04118382907090228</v>
       </c>
       <c r="G104">
-        <v>1.680274718869417</v>
+        <v>2.587187485518128</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6917,32 +6917,32 @@
         </is>
       </c>
       <c r="O104">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B105">
-        <v>0.4055381538619405</v>
+        <v>0.2664097623400104</v>
       </c>
       <c r="C105">
-        <v>0.6281648888325391</v>
+        <v>0.8977750450309833</v>
       </c>
       <c r="D105">
-        <v>-1.436788867052769</v>
+        <v>-1.473330878250489</v>
       </c>
       <c r="E105">
-        <v>0.1507779947045666</v>
+        <v>0.1406618384644878</v>
       </c>
       <c r="F105">
-        <v>0.1183959364775185</v>
+        <v>0.0458524590121322</v>
       </c>
       <c r="G105">
-        <v>1.3890780303003</v>
+        <v>1.547881247792656</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6980,32 +6980,32 @@
         </is>
       </c>
       <c r="O105">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
       <c r="B106">
-        <v>0.3777416028313139</v>
+        <v>0.2943694548550703</v>
       </c>
       <c r="C106">
-        <v>0.600586313648665</v>
+        <v>0.8531945886892135</v>
       </c>
       <c r="D106">
-        <v>-1.620990830769842</v>
+        <v>-1.433342015539568</v>
       </c>
       <c r="E106">
-        <v>0.1050196051853645</v>
+        <v>0.1517601203511784</v>
       </c>
       <c r="F106">
-        <v>0.1164058541145176</v>
+        <v>0.05529071333393965</v>
       </c>
       <c r="G106">
-        <v>1.225786448585274</v>
+        <v>1.567232012875479</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -7043,32 +7043,32 @@
         </is>
       </c>
       <c r="O106">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B107">
-        <v>0.3770195383907583</v>
+        <v>0.1546236768100691</v>
       </c>
       <c r="C107">
-        <v>0.4846861800935345</v>
+        <v>0.8067067296885065</v>
       </c>
       <c r="D107">
-        <v>-2.012556385904424</v>
+        <v>-2.314051608866039</v>
       </c>
       <c r="E107">
-        <v>0.04416131915188909</v>
+        <v>0.02066489138227803</v>
       </c>
       <c r="F107">
-        <v>0.1458136673075164</v>
+        <v>0.03181309943831227</v>
       </c>
       <c r="G107">
-        <v>0.9748313375083273</v>
+        <v>0.7515294596373689</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -7106,32 +7106,32 @@
         </is>
       </c>
       <c r="O107">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B108">
-        <v>0.5869649541983387</v>
+        <v>0.4390419659090566</v>
       </c>
       <c r="C108">
-        <v>0.5613106596793725</v>
+        <v>0.926230032001207</v>
       </c>
       <c r="D108">
-        <v>-0.9491894639597858</v>
+        <v>-0.8887212114807245</v>
       </c>
       <c r="E108">
-        <v>0.3425242592191698</v>
+        <v>0.3741529284201189</v>
       </c>
       <c r="F108">
-        <v>0.1953546134781873</v>
+        <v>0.07146569173805041</v>
       </c>
       <c r="G108">
-        <v>1.7636023604609</v>
+        <v>2.697208172780608</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -7169,32 +7169,32 @@
         </is>
       </c>
       <c r="O108">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B109">
-        <v>0.533873613756585</v>
+        <v>0.3390285799832226</v>
       </c>
       <c r="C109">
-        <v>0.5443289605999346</v>
+        <v>0.7796715500498083</v>
       </c>
       <c r="D109">
-        <v>-1.152972176423301</v>
+        <v>-1.387341718895641</v>
       </c>
       <c r="E109">
-        <v>0.248921804932807</v>
+        <v>0.1653375874756335</v>
       </c>
       <c r="F109">
-        <v>0.1836981596750493</v>
+        <v>0.07354932375840291</v>
       </c>
       <c r="G109">
-        <v>1.551572623099219</v>
+        <v>1.562765939534673</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="O109">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="110">
@@ -7242,22 +7242,22 @@
         </is>
       </c>
       <c r="B110">
-        <v>0.8389711730998016</v>
+        <v>0.9851976409170731</v>
       </c>
       <c r="C110">
-        <v>0.2949959113923422</v>
+        <v>0.3449818860214863</v>
       </c>
       <c r="D110">
-        <v>-0.5951910686421685</v>
+        <v>-0.04322837767645166</v>
       </c>
       <c r="E110">
-        <v>0.5517157597104831</v>
+        <v>0.9655194841120598</v>
       </c>
       <c r="F110">
-        <v>0.4705936511907612</v>
+        <v>0.5010421352284434</v>
       </c>
       <c r="G110">
-        <v>1.49571212342415</v>
+        <v>1.937191153047492</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="O110">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="111">
@@ -7305,22 +7305,22 @@
         </is>
       </c>
       <c r="B111">
-        <v>0.657512359061553</v>
+        <v>0.5471804696248483</v>
       </c>
       <c r="C111">
-        <v>0.3643189682191732</v>
+        <v>0.371665857532603</v>
       </c>
       <c r="D111">
-        <v>-1.150891813579258</v>
+        <v>-1.622362109850018</v>
       </c>
       <c r="E111">
-        <v>0.2497767460924974</v>
+        <v>0.1047258370778103</v>
       </c>
       <c r="F111">
-        <v>0.3219549098871333</v>
+        <v>0.2640997781154599</v>
       </c>
       <c r="G111">
-        <v>1.342804501631134</v>
+        <v>1.133686928763621</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="O111">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="112">
@@ -7368,22 +7368,22 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.9806044104012832</v>
+        <v>1.221758860406002</v>
       </c>
       <c r="C112">
-        <v>0.3776727243667305</v>
+        <v>0.3617907468794859</v>
       </c>
       <c r="D112">
-        <v>-0.05186011818077187</v>
+        <v>0.5536114759552889</v>
       </c>
       <c r="E112">
-        <v>0.9586401525701999</v>
+        <v>0.5798447704660707</v>
       </c>
       <c r="F112">
-        <v>0.4677547823035861</v>
+        <v>0.6012134048933757</v>
       </c>
       <c r="G112">
-        <v>2.055745972201204</v>
+        <v>2.482803445218092</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="O112">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="113">
@@ -7431,22 +7431,22 @@
         </is>
       </c>
       <c r="B113">
-        <v>0.9135651903854597</v>
+        <v>0.7725458369284666</v>
       </c>
       <c r="C113">
-        <v>0.2851178065034172</v>
+        <v>0.3247023493872266</v>
       </c>
       <c r="D113">
-        <v>-0.3170638253254429</v>
+        <v>-0.794770769684363</v>
       </c>
       <c r="E113">
-        <v>0.7511951729979323</v>
+        <v>0.4267468571192008</v>
       </c>
       <c r="F113">
-        <v>0.5224525176956919</v>
+        <v>0.4088246895908939</v>
       </c>
       <c r="G113">
-        <v>1.597468341745352</v>
+        <v>1.459860633057027</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -7484,32 +7484,32 @@
         </is>
       </c>
       <c r="O113">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.7412765119039287</v>
+        <v>0.8165828423198053</v>
       </c>
       <c r="C114">
-        <v>0.3987412415528366</v>
+        <v>0.6181038518642989</v>
       </c>
       <c r="D114">
-        <v>-0.750816649070619</v>
+        <v>-0.3278201726550595</v>
       </c>
       <c r="E114">
-        <v>0.4527630081944006</v>
+        <v>0.7430476338548813</v>
       </c>
       <c r="F114">
-        <v>0.3392900151480213</v>
+        <v>0.2431472140849401</v>
       </c>
       <c r="G114">
-        <v>1.619531499801815</v>
+        <v>2.742402543580665</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7547,32 +7547,32 @@
         </is>
       </c>
       <c r="O114">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B115">
-        <v>0.6491970412216176</v>
+        <v>0.4139119788364118</v>
       </c>
       <c r="C115">
-        <v>0.4265721385335192</v>
+        <v>0.63160395259102</v>
       </c>
       <c r="D115">
-        <v>-1.012768912694016</v>
+        <v>-1.396606109967283</v>
       </c>
       <c r="E115">
-        <v>0.311170552830375</v>
+        <v>0.162532051932595</v>
       </c>
       <c r="F115">
-        <v>0.2813699213658464</v>
+        <v>0.1200288751567572</v>
       </c>
       <c r="G115">
-        <v>1.497874386448404</v>
+        <v>1.427349260755189</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7610,32 +7610,32 @@
         </is>
       </c>
       <c r="O115">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B116">
-        <v>1.015155474815483</v>
+        <v>1.333088463806502</v>
       </c>
       <c r="C116">
-        <v>0.4523809092013106</v>
+        <v>0.6221470290226467</v>
       </c>
       <c r="D116">
-        <v>0.03325024910533008</v>
+        <v>0.4621068493924637</v>
       </c>
       <c r="E116">
-        <v>0.9734750272618041</v>
+        <v>0.6440046986005215</v>
       </c>
       <c r="F116">
-        <v>0.4182782025899252</v>
+        <v>0.3938097451917275</v>
       </c>
       <c r="G116">
-        <v>2.463768448049345</v>
+        <v>4.512648236952034</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7673,32 +7673,32 @@
         </is>
       </c>
       <c r="O116">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B117">
-        <v>0.8874369659801357</v>
+        <v>0.6902345401213671</v>
       </c>
       <c r="C117">
-        <v>0.3766739476247111</v>
+        <v>0.5835735489591104</v>
       </c>
       <c r="D117">
-        <v>-0.3170322374448382</v>
+        <v>-0.6352649577591556</v>
       </c>
       <c r="E117">
-        <v>0.7512191410658755</v>
+        <v>0.5252556240578261</v>
       </c>
       <c r="F117">
-        <v>0.4241427713014788</v>
+        <v>0.2199165848682083</v>
       </c>
       <c r="G117">
-        <v>1.856790736221803</v>
+        <v>2.166383770746834</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7736,32 +7736,32 @@
         </is>
       </c>
       <c r="O117">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.7007515116387728</v>
+        <v>0.769387411223269</v>
       </c>
       <c r="C118">
-        <v>0.3115078408819402</v>
+        <v>0.3751144187670963</v>
       </c>
       <c r="D118">
-        <v>-1.141550500815909</v>
+        <v>-0.6988818277623243</v>
       </c>
       <c r="E118">
-        <v>0.2536409091435334</v>
+        <v>0.4846258850204183</v>
       </c>
       <c r="F118">
-        <v>0.3805468123254068</v>
+        <v>0.3688477205799536</v>
       </c>
       <c r="G118">
-        <v>1.290387056623468</v>
+        <v>1.604881785952444</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7799,32 +7799,32 @@
         </is>
       </c>
       <c r="O118">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B119">
-        <v>0.6715717491371309</v>
+        <v>0.5481203967304542</v>
       </c>
       <c r="C119">
-        <v>0.360944461812236</v>
+        <v>0.3950267021311524</v>
       </c>
       <c r="D119">
-        <v>-1.103035125342427</v>
+        <v>-1.522075117602022</v>
       </c>
       <c r="E119">
-        <v>0.2700119116728206</v>
+        <v>0.1279902598594038</v>
       </c>
       <c r="F119">
-        <v>0.3310212966813174</v>
+        <v>0.2527136060822713</v>
       </c>
       <c r="G119">
-        <v>1.362476126946306</v>
+        <v>1.18883970661296</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7862,32 +7862,32 @@
         </is>
       </c>
       <c r="O119">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.8198918529244443</v>
+        <v>0.9959444875890063</v>
       </c>
       <c r="C120">
-        <v>0.380107432391216</v>
+        <v>0.3863414001160071</v>
       </c>
       <c r="D120">
-        <v>-0.5224387033157809</v>
+        <v>-0.01051856803851285</v>
       </c>
       <c r="E120">
-        <v>0.60136491437074</v>
+        <v>0.9916075517177305</v>
       </c>
       <c r="F120">
-        <v>0.3892320001050504</v>
+        <v>0.4670686694806404</v>
       </c>
       <c r="G120">
-        <v>1.727048778904231</v>
+        <v>2.123682206005989</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7925,32 +7925,32 @@
         </is>
       </c>
       <c r="O120">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B121">
-        <v>0.9766236433897635</v>
+        <v>0.8595439817121682</v>
       </c>
       <c r="C121">
-        <v>0.2889359496156398</v>
+        <v>0.3540885481671536</v>
       </c>
       <c r="D121">
-        <v>-0.08186560993064529</v>
+        <v>-0.4274447309164887</v>
       </c>
       <c r="E121">
-        <v>0.9347535819127498</v>
+        <v>0.6690554329547556</v>
       </c>
       <c r="F121">
-        <v>0.5543505820301476</v>
+        <v>0.4294052849158937</v>
       </c>
       <c r="G121">
-        <v>1.720560547325312</v>
+        <v>1.720556039831503</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="O121">
-        <v>7656</v>
+        <v>7621</v>
       </c>
     </row>
     <row r="122">
@@ -7998,22 +7998,22 @@
         </is>
       </c>
       <c r="B122">
-        <v>0.6613405528446947</v>
+        <v>0.5895285699519446</v>
       </c>
       <c r="C122">
-        <v>0.3032026942507112</v>
+        <v>0.296167007463366</v>
       </c>
       <c r="D122">
-        <v>-1.363729185477723</v>
+        <v>-1.784236873600082</v>
       </c>
       <c r="E122">
-        <v>0.1726528149353355</v>
+        <v>0.0743851829508059</v>
       </c>
       <c r="F122">
-        <v>0.3650384005263215</v>
+        <v>0.3299187841336835</v>
       </c>
       <c r="G122">
-        <v>1.198151553936007</v>
+        <v>1.053422695231441</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="O122">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="123">
@@ -8061,22 +8061,22 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.7205841152410665</v>
+        <v>0.7204103587492192</v>
       </c>
       <c r="C123">
-        <v>0.1771781329907702</v>
+        <v>0.1560891221656237</v>
       </c>
       <c r="D123">
-        <v>-1.849512234805742</v>
+        <v>-2.100942602986005</v>
       </c>
       <c r="E123">
-        <v>0.06438388279165694</v>
+        <v>0.03564600501278676</v>
       </c>
       <c r="F123">
-        <v>0.5091788829374742</v>
+        <v>0.5305381848992491</v>
       </c>
       <c r="G123">
-        <v>1.019762375340912</v>
+        <v>0.9782351200446331</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="O123">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="124">
@@ -8124,22 +8124,22 @@
         </is>
       </c>
       <c r="B124">
-        <v>0.8713811899485108</v>
+        <v>0.8431277144749584</v>
       </c>
       <c r="C124">
-        <v>0.2890044621822435</v>
+        <v>0.2805055890781052</v>
       </c>
       <c r="D124">
-        <v>-0.4763793282114979</v>
+        <v>-0.6083188325970776</v>
       </c>
       <c r="E124">
-        <v>0.6338041590578923</v>
+        <v>0.5429760329168474</v>
       </c>
       <c r="F124">
-        <v>0.4945465045345454</v>
+        <v>0.4865489895213165</v>
       </c>
       <c r="G124">
-        <v>1.535356475546666</v>
+        <v>1.461033438000024</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -8177,32 +8177,32 @@
         </is>
       </c>
       <c r="O124">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B125">
-        <v>0.5452368535151955</v>
+        <v>0.3139158246850947</v>
       </c>
       <c r="C125">
-        <v>0.3638564979564509</v>
+        <v>0.5470558026193205</v>
       </c>
       <c r="D125">
-        <v>-1.666962081282038</v>
+        <v>-2.117938239053384</v>
       </c>
       <c r="E125">
-        <v>0.09552194501163612</v>
+        <v>0.03418029858447304</v>
       </c>
       <c r="F125">
-        <v>0.2672206341577421</v>
+        <v>0.1074381362368799</v>
       </c>
       <c r="G125">
-        <v>1.112501013883765</v>
+        <v>0.9172082506201978</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8240,32 +8240,32 @@
         </is>
       </c>
       <c r="O125">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.7095650181847213</v>
+        <v>0.544838694792199</v>
       </c>
       <c r="C126">
-        <v>0.1849205649611703</v>
+        <v>0.2523292930434567</v>
       </c>
       <c r="D126">
-        <v>-1.855408278737656</v>
+        <v>-2.406638934629241</v>
       </c>
       <c r="E126">
-        <v>0.06353794607569187</v>
+        <v>0.01610007874824734</v>
       </c>
       <c r="F126">
-        <v>0.4938414353154542</v>
+        <v>0.3322652020455969</v>
       </c>
       <c r="G126">
-        <v>1.019522622094015</v>
+        <v>0.8934104489886673</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8303,32 +8303,32 @@
         </is>
       </c>
       <c r="O126">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B127">
-        <v>0.7180607047092055</v>
+        <v>0.5321714487635403</v>
       </c>
       <c r="C127">
-        <v>0.3415003420481111</v>
+        <v>0.5201781374735761</v>
       </c>
       <c r="D127">
-        <v>-0.9698413904147437</v>
+        <v>-1.212641447237141</v>
       </c>
       <c r="E127">
-        <v>0.3321255579979546</v>
+        <v>0.2252669351608937</v>
       </c>
       <c r="F127">
-        <v>0.3676846867145712</v>
+        <v>0.1919884654691635</v>
       </c>
       <c r="G127">
-        <v>1.40231887342032</v>
+        <v>1.475122217300981</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8366,32 +8366,32 @@
         </is>
       </c>
       <c r="O127">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B128">
-        <v>0.585948126961886</v>
+        <v>0.3616442095082134</v>
       </c>
       <c r="C128">
-        <v>0.3122201626257182</v>
+        <v>0.4599717426959116</v>
       </c>
       <c r="D128">
-        <v>-1.712009914321035</v>
+        <v>-2.21121060865178</v>
       </c>
       <c r="E128">
-        <v>0.08689484139994028</v>
+        <v>0.02702125609277064</v>
       </c>
       <c r="F128">
-        <v>0.3177582873625894</v>
+        <v>0.1468090602004682</v>
       </c>
       <c r="G128">
-        <v>1.080491748428791</v>
+        <v>0.8908614638104159</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8429,32 +8429,32 @@
         </is>
       </c>
       <c r="O128">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.7174447785874237</v>
+        <v>0.5807525782284985</v>
       </c>
       <c r="C129">
-        <v>0.1745903282847528</v>
+        <v>0.2345396917124972</v>
       </c>
       <c r="D129">
-        <v>-1.901934094595745</v>
+        <v>-2.317008536562665</v>
       </c>
       <c r="E129">
-        <v>0.05717977118955963</v>
+        <v>0.0205032667526581</v>
       </c>
       <c r="F129">
-        <v>0.5095384039300479</v>
+        <v>0.3667335132698535</v>
       </c>
       <c r="G129">
-        <v>1.010182954517834</v>
+        <v>0.9196693100444088</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8492,32 +8492,32 @@
         </is>
       </c>
       <c r="O129">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B130">
-        <v>0.7809803965061484</v>
+        <v>0.6129111919994301</v>
       </c>
       <c r="C130">
-        <v>0.2919483420180701</v>
+        <v>0.4367784648777006</v>
       </c>
       <c r="D130">
-        <v>-0.8467430513664803</v>
+        <v>-1.120786090192174</v>
       </c>
       <c r="E130">
-        <v>0.3971383568086485</v>
+        <v>0.2623789264066959</v>
       </c>
       <c r="F130">
-        <v>0.4406900585683278</v>
+        <v>0.2603820539374821</v>
       </c>
       <c r="G130">
-        <v>1.384034806023047</v>
+        <v>1.442726653382796</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="O130">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="131">
@@ -8565,22 +8565,22 @@
         </is>
       </c>
       <c r="B131">
-        <v>0.7400938708063024</v>
+        <v>0.6969672636365177</v>
       </c>
       <c r="C131">
-        <v>0.2046877215748864</v>
+        <v>0.1910414230326271</v>
       </c>
       <c r="D131">
-        <v>-1.470426491986468</v>
+        <v>-1.889730672629546</v>
       </c>
       <c r="E131">
-        <v>0.1414462807520657</v>
+        <v>0.05879398967965845</v>
       </c>
       <c r="F131">
-        <v>0.4955144264247852</v>
+        <v>0.4792891810125082</v>
       </c>
       <c r="G131">
-        <v>1.105394532217919</v>
+        <v>1.013507890069186</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         </is>
       </c>
       <c r="O131">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="132">
@@ -8628,22 +8628,22 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.7254482780186116</v>
+        <v>0.7487748293916427</v>
       </c>
       <c r="C132">
-        <v>0.1703196824800616</v>
+        <v>0.1517348578580728</v>
       </c>
       <c r="D132">
-        <v>-1.884488604153321</v>
+        <v>-1.906727122971629</v>
       </c>
       <c r="E132">
-        <v>0.05949891483388963</v>
+        <v>0.05655593279790666</v>
       </c>
       <c r="F132">
-        <v>0.5195532640662817</v>
+        <v>0.5561530095386428</v>
       </c>
       <c r="G132">
-        <v>1.012937922786353</v>
+        <v>1.008110601784899</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="O132">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="133">
@@ -8691,22 +8691,22 @@
         </is>
       </c>
       <c r="B133">
-        <v>0.9440295156034595</v>
+        <v>0.9520661429918645</v>
       </c>
       <c r="C133">
-        <v>0.1896676478865171</v>
+        <v>0.1730935175678672</v>
       </c>
       <c r="D133">
-        <v>-0.3036777618015166</v>
+        <v>-0.28378167687511</v>
       </c>
       <c r="E133">
-        <v>0.7613734018810607</v>
+        <v>0.7765776972435114</v>
       </c>
       <c r="F133">
-        <v>0.6509388291119155</v>
+        <v>0.6781560677820164</v>
       </c>
       <c r="G133">
-        <v>1.369086750511361</v>
+        <v>1.336609644437723</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8744,32 +8744,32 @@
         </is>
       </c>
       <c r="O133">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B134">
-        <v>0.6663499224575773</v>
+        <v>0.4670941620797316</v>
       </c>
       <c r="C134">
-        <v>0.2999226413959544</v>
+        <v>0.42227233217571</v>
       </c>
       <c r="D134">
-        <v>-1.353483469723779</v>
+        <v>-1.802685972471153</v>
       </c>
       <c r="E134">
-        <v>0.1759012274277716</v>
+        <v>0.07143754642738818</v>
       </c>
       <c r="F134">
-        <v>0.370175555106645</v>
+        <v>0.2041576126317915</v>
       </c>
       <c r="G134">
-        <v>1.199490925410511</v>
+        <v>1.068669218044099</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8807,32 +8807,32 @@
         </is>
       </c>
       <c r="O134">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.7191860348303284</v>
+        <v>0.6151040444316614</v>
       </c>
       <c r="C135">
-        <v>0.1796904100693014</v>
+        <v>0.2350222228096295</v>
       </c>
       <c r="D135">
-        <v>-1.834461914413068</v>
+        <v>-2.067735730423108</v>
       </c>
       <c r="E135">
-        <v>0.06658545626374825</v>
+        <v>0.03866488010302133</v>
       </c>
       <c r="F135">
-        <v>0.5056948040278355</v>
+        <v>0.3880585922445316</v>
       </c>
       <c r="G135">
-        <v>1.022807726271397</v>
+        <v>0.9749893264514337</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8870,32 +8870,32 @@
         </is>
       </c>
       <c r="O135">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B136">
-        <v>0.8455086752260741</v>
+        <v>0.7380384212652947</v>
       </c>
       <c r="C136">
-        <v>0.2840867537033693</v>
+        <v>0.4023704126736846</v>
       </c>
       <c r="D136">
-        <v>-0.5907239532995532</v>
+        <v>-0.7549247778515582</v>
       </c>
       <c r="E136">
-        <v>0.5547053957868588</v>
+        <v>0.4502941177731628</v>
       </c>
       <c r="F136">
-        <v>0.4845102674778108</v>
+        <v>0.3354135899811125</v>
       </c>
       <c r="G136">
-        <v>1.475479402333389</v>
+        <v>1.623967327306092</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8933,32 +8933,32 @@
         </is>
       </c>
       <c r="O136">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B137">
-        <v>0.690059446155674</v>
+        <v>0.6105195804948748</v>
       </c>
       <c r="C137">
-        <v>0.2321178353473759</v>
+        <v>0.2358520164007349</v>
       </c>
       <c r="D137">
-        <v>-1.598229324764607</v>
+        <v>-2.092180175490271</v>
       </c>
       <c r="E137">
-        <v>0.1099919496998868</v>
+        <v>0.03642240119795991</v>
       </c>
       <c r="F137">
-        <v>0.4378319453256428</v>
+        <v>0.3845404204363975</v>
       </c>
       <c r="G137">
-        <v>1.087590899459173</v>
+        <v>0.9692977340188028</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8996,32 +8996,32 @@
         </is>
       </c>
       <c r="O137">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.7098287693714356</v>
+        <v>0.7113442351087553</v>
       </c>
       <c r="C138">
-        <v>0.170030387842078</v>
+        <v>0.1628842187217447</v>
       </c>
       <c r="D138">
-        <v>-2.015707381968826</v>
+        <v>-2.091048554283016</v>
       </c>
       <c r="E138">
-        <v>0.0438305832485717</v>
+        <v>0.03652371170034316</v>
       </c>
       <c r="F138">
-        <v>0.5086551767416414</v>
+        <v>0.5169309293070036</v>
       </c>
       <c r="G138">
-        <v>0.99056670386211</v>
+        <v>0.9788747241354213</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -9059,32 +9059,32 @@
         </is>
       </c>
       <c r="O138">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B139">
-        <v>0.9071610800151522</v>
+        <v>0.8800916685671285</v>
       </c>
       <c r="C139">
-        <v>0.2110305477210266</v>
+        <v>0.2179233782110026</v>
       </c>
       <c r="D139">
-        <v>-0.461711582512708</v>
+        <v>-0.5861198057655164</v>
       </c>
       <c r="E139">
-        <v>0.6442881639132669</v>
+        <v>0.5577950075834898</v>
       </c>
       <c r="F139">
-        <v>0.5998668762393957</v>
+        <v>0.5741577005332247</v>
       </c>
       <c r="G139">
-        <v>1.371873089998449</v>
+        <v>1.349039374307671</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="O139">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="140">
@@ -9132,22 +9132,22 @@
         </is>
       </c>
       <c r="B140">
-        <v>0.4892047796152979</v>
+        <v>0.3546127846458775</v>
       </c>
       <c r="C140">
-        <v>0.4732512534867317</v>
+        <v>0.5372308654321118</v>
       </c>
       <c r="D140">
-        <v>-1.510770652334893</v>
+        <v>-1.929764090243022</v>
       </c>
       <c r="E140">
-        <v>0.1308468943713643</v>
+        <v>0.05363607477210255</v>
       </c>
       <c r="F140">
-        <v>0.1934899864582961</v>
+        <v>0.1237264770666815</v>
       </c>
       <c r="G140">
-        <v>1.236866676043901</v>
+        <v>1.016356644233322</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="O140">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="141">
@@ -9195,22 +9195,22 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.18845762668438</v>
+        <v>1.21929465603107</v>
       </c>
       <c r="C141">
-        <v>0.3880000384981105</v>
+        <v>0.3771685011848585</v>
       </c>
       <c r="D141">
-        <v>0.4449905600065054</v>
+        <v>0.525686901569139</v>
       </c>
       <c r="E141">
-        <v>0.6563265761310009</v>
+        <v>0.5991057660860841</v>
       </c>
       <c r="F141">
-        <v>0.5555427322921548</v>
+        <v>0.5821866735960837</v>
       </c>
       <c r="G141">
-        <v>2.542435438938449</v>
+        <v>2.553613000178995</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="O141">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="142">
@@ -9258,22 +9258,22 @@
         </is>
       </c>
       <c r="B142">
-        <v>0.9205611231421155</v>
+        <v>0.6453762786792314</v>
       </c>
       <c r="C142">
-        <v>0.4469556812144875</v>
+        <v>0.5040123261653587</v>
       </c>
       <c r="D142">
-        <v>-0.1851903485794547</v>
+        <v>-0.8688711203148374</v>
       </c>
       <c r="E142">
-        <v>0.8530797388802733</v>
+        <v>0.3849176272961213</v>
       </c>
       <c r="F142">
-        <v>0.3833568822322334</v>
+        <v>0.2403238809278292</v>
       </c>
       <c r="G142">
-        <v>2.210558413628029</v>
+        <v>1.733121733361712</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -9311,32 +9311,32 @@
         </is>
       </c>
       <c r="O142">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
       <c r="B143">
-        <v>0.4768841811711296</v>
+        <v>0.2197380695487179</v>
       </c>
       <c r="C143">
-        <v>0.5205219704155124</v>
+        <v>0.8637275798969258</v>
       </c>
       <c r="D143">
-        <v>-1.422575158074797</v>
+        <v>-1.754394638052246</v>
       </c>
       <c r="E143">
-        <v>0.1548593496459517</v>
+        <v>0.07936290947256472</v>
       </c>
       <c r="F143">
-        <v>0.1719268919169088</v>
+        <v>0.04042956381798265</v>
       </c>
       <c r="G143">
-        <v>1.322762947178553</v>
+        <v>1.194294834007599</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -9374,32 +9374,32 @@
         </is>
       </c>
       <c r="O143">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
       <c r="B144">
-        <v>1.146015370982163</v>
+        <v>1.240124148153173</v>
       </c>
       <c r="C144">
-        <v>0.4187630969198077</v>
+        <v>0.5923182392595764</v>
       </c>
       <c r="D144">
-        <v>0.3254609394416106</v>
+        <v>0.3633376111340319</v>
       </c>
       <c r="E144">
-        <v>0.7448322405827632</v>
+        <v>0.7163527006778974</v>
       </c>
       <c r="F144">
-        <v>0.504357691593357</v>
+        <v>0.3884033481442758</v>
       </c>
       <c r="G144">
-        <v>2.604007537543984</v>
+        <v>3.95956396921008</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9437,32 +9437,32 @@
         </is>
       </c>
       <c r="O144">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
       <c r="B145">
-        <v>0.8390786110780089</v>
+        <v>0.4825228768735469</v>
       </c>
       <c r="C145">
-        <v>0.48069972059509</v>
+        <v>0.8088508532162655</v>
       </c>
       <c r="D145">
-        <v>-0.3649906027139252</v>
+        <v>-0.9009410612846334</v>
       </c>
       <c r="E145">
-        <v>0.7151184210221498</v>
+        <v>0.3676196577330573</v>
       </c>
       <c r="F145">
-        <v>0.3270621645519368</v>
+        <v>0.09886050258745648</v>
       </c>
       <c r="G145">
-        <v>2.152657787650636</v>
+        <v>2.355119796203278</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9500,32 +9500,32 @@
         </is>
       </c>
       <c r="O145">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
       <c r="B146">
-        <v>0.5019353509535602</v>
+        <v>0.2351503288826194</v>
       </c>
       <c r="C146">
-        <v>0.4530629135122829</v>
+        <v>0.7546635474890941</v>
       </c>
       <c r="D146">
-        <v>-1.521386831689974</v>
+        <v>-1.918113411997281</v>
       </c>
       <c r="E146">
-        <v>0.1281627914606239</v>
+        <v>0.05509663220215912</v>
       </c>
       <c r="F146">
-        <v>0.206537983555556</v>
+        <v>0.05357655863269874</v>
       </c>
       <c r="G146">
-        <v>1.219819677716111</v>
+        <v>1.032087140062335</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9563,32 +9563,32 @@
         </is>
       </c>
       <c r="O146">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
       <c r="B147">
-        <v>1.14447235424656</v>
+        <v>1.291693519163865</v>
       </c>
       <c r="C147">
-        <v>0.3851186254594779</v>
+        <v>0.5456673382815994</v>
       </c>
       <c r="D147">
-        <v>0.3503951662860784</v>
+        <v>0.4690663065105652</v>
       </c>
       <c r="E147">
-        <v>0.7260421534956409</v>
+        <v>0.6390222417793004</v>
       </c>
       <c r="F147">
-        <v>0.5380117220458459</v>
+        <v>0.4432886381939662</v>
       </c>
       <c r="G147">
-        <v>2.43455098832038</v>
+        <v>3.763850466024963</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -9626,32 +9626,32 @@
         </is>
       </c>
       <c r="O147">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
       <c r="B148">
-        <v>0.9348856423105201</v>
+        <v>0.5370053015956342</v>
       </c>
       <c r="C148">
-        <v>0.4181909734691353</v>
+        <v>0.7096037311908799</v>
       </c>
       <c r="D148">
-        <v>-0.1610055432435059</v>
+        <v>-0.8761894626188077</v>
       </c>
       <c r="E148">
-        <v>0.8720890347271069</v>
+        <v>0.3809270440345996</v>
       </c>
       <c r="F148">
-        <v>0.4119017983667084</v>
+        <v>0.1336480979152093</v>
       </c>
       <c r="G148">
-        <v>2.121892081229124</v>
+        <v>2.157716409288311</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -9689,7 +9689,7 @@
         </is>
       </c>
       <c r="O148">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="149">
@@ -9699,22 +9699,22 @@
         </is>
       </c>
       <c r="B149">
-        <v>0.5816992454393196</v>
+        <v>0.5417019046971395</v>
       </c>
       <c r="C149">
-        <v>0.3028087114027582</v>
+        <v>0.2898665568368094</v>
       </c>
       <c r="D149">
-        <v>-1.789254089557159</v>
+        <v>-2.114902204886044</v>
       </c>
       <c r="E149">
-        <v>0.07357390419996335</v>
+        <v>0.03443828323733833</v>
       </c>
       <c r="F149">
-        <v>0.3213270285955972</v>
+        <v>0.3069202209128086</v>
       </c>
       <c r="G149">
-        <v>1.053051819585743</v>
+        <v>0.9560821788795434</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="O149">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="150">
@@ -9762,22 +9762,22 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.084169769662375</v>
+        <v>1.232976400651978</v>
       </c>
       <c r="C150">
-        <v>0.3370404132640267</v>
+        <v>0.3025373961572602</v>
       </c>
       <c r="D150">
-        <v>0.2397768981226703</v>
+        <v>0.6922485844056072</v>
       </c>
       <c r="E150">
-        <v>0.81050321722251</v>
+        <v>0.4887812326979488</v>
       </c>
       <c r="F150">
-        <v>0.560025720693671</v>
+        <v>0.6814507372498966</v>
       </c>
       <c r="G150">
-        <v>2.098875187364319</v>
+        <v>2.230874106468564</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="O150">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="151">
@@ -9825,22 +9825,22 @@
         </is>
       </c>
       <c r="B151">
-        <v>0.8560112218301209</v>
+        <v>0.765383553746244</v>
       </c>
       <c r="C151">
-        <v>0.2638086925662445</v>
+        <v>0.254471503659204</v>
       </c>
       <c r="D151">
-        <v>-0.5893353695032539</v>
+        <v>-1.050719587507477</v>
       </c>
       <c r="E151">
-        <v>0.5556363226803475</v>
+        <v>0.2933873971017112</v>
       </c>
       <c r="F151">
-        <v>0.5104169544432746</v>
+        <v>0.4648069245599139</v>
       </c>
       <c r="G151">
-        <v>1.435601238399951</v>
+        <v>1.260334029876782</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -9878,32 +9878,32 @@
         </is>
       </c>
       <c r="O151">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
       <c r="B152">
-        <v>0.5948663844803019</v>
+        <v>0.3842422121067757</v>
       </c>
       <c r="C152">
-        <v>0.4125208960115334</v>
+        <v>0.5912487541246387</v>
       </c>
       <c r="D152">
-        <v>-1.259132488985201</v>
+        <v>-1.617732228394624</v>
       </c>
       <c r="E152">
-        <v>0.2079824812433992</v>
+        <v>0.1057203173154191</v>
       </c>
       <c r="F152">
-        <v>0.2650214370852992</v>
+        <v>0.1205960885417234</v>
       </c>
       <c r="G152">
-        <v>1.33523544086274</v>
+        <v>1.224269205991931</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9941,32 +9941,32 @@
         </is>
       </c>
       <c r="O152">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
       <c r="B153">
-        <v>1.20760634931838</v>
+        <v>1.507949119336869</v>
       </c>
       <c r="C153">
-        <v>0.3871947223136821</v>
+        <v>0.4957053818215057</v>
       </c>
       <c r="D153">
-        <v>0.4871971795192852</v>
+        <v>0.8286182550901824</v>
       </c>
       <c r="E153">
-        <v>0.6261186039210176</v>
+        <v>0.4073204548741716</v>
       </c>
       <c r="F153">
-        <v>0.5653854691917718</v>
+        <v>0.5707441936660197</v>
       </c>
       <c r="G153">
-        <v>2.579325388391653</v>
+        <v>3.984115075972993</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -10004,32 +10004,32 @@
         </is>
       </c>
       <c r="O153">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
       <c r="B154">
-        <v>0.8875430201177299</v>
+        <v>0.6456298110461606</v>
       </c>
       <c r="C154">
-        <v>0.3759576662392924</v>
+        <v>0.5480255622180049</v>
       </c>
       <c r="D154">
-        <v>-0.3173184008418125</v>
+        <v>-0.798373319667079</v>
       </c>
       <c r="E154">
-        <v>0.751002016436299</v>
+        <v>0.4246538813595064</v>
       </c>
       <c r="F154">
-        <v>0.4247893963080461</v>
+        <v>0.2205481254446041</v>
       </c>
       <c r="G154">
-        <v>1.854407429672416</v>
+        <v>1.89000859595245</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -10067,32 +10067,32 @@
         </is>
       </c>
       <c r="O154">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
       <c r="B155">
-        <v>0.5615596162844282</v>
+        <v>0.475400090832191</v>
       </c>
       <c r="C155">
-        <v>0.3283925378486122</v>
+        <v>0.3415220955574819</v>
       </c>
       <c r="D155">
-        <v>-1.757157275746393</v>
+        <v>-2.177307245018756</v>
       </c>
       <c r="E155">
-        <v>0.0788910053225836</v>
+        <v>0.02945765098450991</v>
       </c>
       <c r="F155">
-        <v>0.2950309879807534</v>
+        <v>0.2434193652410956</v>
       </c>
       <c r="G155">
-        <v>1.068868069757087</v>
+        <v>0.9284604211312756</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10130,32 +10130,32 @@
         </is>
       </c>
       <c r="O155">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.9847745925974204</v>
+        <v>1.150306335024613</v>
       </c>
       <c r="C156">
-        <v>0.3418614267115022</v>
+        <v>0.3259837668107826</v>
       </c>
       <c r="D156">
-        <v>-0.0448793072331127</v>
+        <v>0.4295560068986956</v>
       </c>
       <c r="E156">
-        <v>0.9642035106587447</v>
+        <v>0.6675186446715887</v>
       </c>
       <c r="F156">
-        <v>0.5038994231542674</v>
+        <v>0.6072054014274353</v>
       </c>
       <c r="G156">
-        <v>1.924552705686507</v>
+        <v>2.179171432413365</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10193,32 +10193,32 @@
         </is>
       </c>
       <c r="O156">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
       <c r="B157">
-        <v>0.9090406164974733</v>
+        <v>0.7563957028491524</v>
       </c>
       <c r="C157">
-        <v>0.2802076373568059</v>
+        <v>0.3043206521175254</v>
       </c>
       <c r="D157">
-        <v>-0.3403387005686059</v>
+        <v>-0.9174225322120744</v>
       </c>
       <c r="E157">
-        <v>0.7336014759171385</v>
+        <v>0.3589212699962488</v>
       </c>
       <c r="F157">
-        <v>0.5248921948601547</v>
+        <v>0.4165919217806751</v>
       </c>
       <c r="G157">
-        <v>1.574332502052672</v>
+        <v>1.373369067847353</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="O157">
-        <v>7660</v>
+        <v>7625</v>
       </c>
     </row>
   </sheetData>
